--- a/research/traditional_assets/database/data/mauritius/mauritius_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_real_estate_general_diversified.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08408489620091834</v>
+        <v>0.08399701885661696</v>
       </c>
       <c r="C2">
-        <v>81.82705168646879</v>
+        <v>81.2836814759689</v>
       </c>
       <c r="D2">
-        <v>79.81705168646879</v>
+        <v>80.0006814759689</v>
       </c>
       <c r="E2">
-        <v>-32.7</v>
+        <v>-31.973</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.7270000000000001</v>
       </c>
       <c r="G2">
         <v>2.01</v>
@@ -1451,28 +1451,28 @@
         <v>3.299</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.03656810000000001</v>
       </c>
       <c r="N2">
-        <v>3.299</v>
+        <v>3.2624319</v>
       </c>
       <c r="O2">
-        <v>0.49485</v>
+        <v>0.489364785</v>
       </c>
       <c r="P2">
-        <v>2.80415</v>
+        <v>2.773067115</v>
       </c>
       <c r="Q2">
-        <v>2.83015</v>
+        <v>2.799067115</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08408489620091834</v>
+        <v>0.08441360490567371</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5315308058798892</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>90.2152422466576</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08399701885661696</v>
+        <v>0.08390914151231559</v>
       </c>
       <c r="C3">
-        <v>81.2836814759689</v>
+        <v>80.74115814354582</v>
       </c>
       <c r="D3">
-        <v>80.0006814759689</v>
+        <v>80.18515814354581</v>
       </c>
       <c r="E3">
-        <v>-31.973</v>
+        <v>-31.246</v>
       </c>
       <c r="F3">
-        <v>0.7270000000000001</v>
+        <v>1.454</v>
       </c>
       <c r="G3">
         <v>2.01</v>
@@ -1533,28 +1533,28 @@
         <v>3.299</v>
       </c>
       <c r="M3">
-        <v>0.03656810000000001</v>
+        <v>0.07313620000000001</v>
       </c>
       <c r="N3">
-        <v>3.2624319</v>
+        <v>3.2258638</v>
       </c>
       <c r="O3">
-        <v>0.489364785</v>
+        <v>0.48387957</v>
       </c>
       <c r="P3">
-        <v>2.773067115</v>
+        <v>2.74198423</v>
       </c>
       <c r="Q3">
-        <v>2.799067115</v>
+        <v>2.76798423</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08441360490567371</v>
+        <v>0.08474902195134244</v>
       </c>
       <c r="T3">
-        <v>0.5315308058798892</v>
+        <v>0.5361479477661667</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>90.2152422466576</v>
+        <v>45.1076211233288</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08390914151231559</v>
+        <v>0.08382126416801419</v>
       </c>
       <c r="C4">
-        <v>80.74115814354582</v>
+        <v>80.19948756128701</v>
       </c>
       <c r="D4">
-        <v>80.18515814354581</v>
+        <v>80.37048756128701</v>
       </c>
       <c r="E4">
-        <v>-31.246</v>
+        <v>-30.519</v>
       </c>
       <c r="F4">
-        <v>1.454</v>
+        <v>2.181</v>
       </c>
       <c r="G4">
         <v>2.01</v>
@@ -1615,28 +1615,28 @@
         <v>3.299</v>
       </c>
       <c r="M4">
-        <v>0.07313620000000001</v>
+        <v>0.1097043</v>
       </c>
       <c r="N4">
-        <v>3.2258638</v>
+        <v>3.1892957</v>
       </c>
       <c r="O4">
-        <v>0.48387957</v>
+        <v>0.478394355</v>
       </c>
       <c r="P4">
-        <v>2.74198423</v>
+        <v>2.710901345</v>
       </c>
       <c r="Q4">
-        <v>2.76798423</v>
+        <v>2.736901345</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08474902195134244</v>
+        <v>0.08509135481238578</v>
       </c>
       <c r="T4">
-        <v>0.5361479477661667</v>
+        <v>0.540860288454223</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>45.1076211233288</v>
+        <v>30.07174741555254</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08382126416801419</v>
+        <v>0.08373338682371283</v>
       </c>
       <c r="C5">
-        <v>80.19948756128701</v>
+        <v>79.6586756556935</v>
       </c>
       <c r="D5">
-        <v>80.37048756128701</v>
+        <v>80.5566756556935</v>
       </c>
       <c r="E5">
-        <v>-30.519</v>
+        <v>-29.792</v>
       </c>
       <c r="F5">
-        <v>2.181</v>
+        <v>2.908</v>
       </c>
       <c r="G5">
         <v>2.01</v>
@@ -1697,28 +1697,28 @@
         <v>3.299</v>
       </c>
       <c r="M5">
-        <v>0.1097043</v>
+        <v>0.1462724</v>
       </c>
       <c r="N5">
-        <v>3.1892957</v>
+        <v>3.1527276</v>
       </c>
       <c r="O5">
-        <v>0.478394355</v>
+        <v>0.4729091400000001</v>
       </c>
       <c r="P5">
-        <v>2.710901345</v>
+        <v>2.67981846</v>
       </c>
       <c r="Q5">
-        <v>2.736901345</v>
+        <v>2.70581846</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08509135481238578</v>
+        <v>0.08544081960803421</v>
       </c>
       <c r="T5">
-        <v>0.540860288454223</v>
+        <v>0.5456708029066138</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.07174741555254</v>
+        <v>22.5538105616644</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08373338682371283</v>
+        <v>0.08364550947941143</v>
       </c>
       <c r="C6">
-        <v>79.6586756556935</v>
+        <v>79.11872840831194</v>
       </c>
       <c r="D6">
-        <v>80.5566756556935</v>
+        <v>80.74372840831194</v>
       </c>
       <c r="E6">
-        <v>-29.792</v>
+        <v>-29.065</v>
       </c>
       <c r="F6">
-        <v>2.908</v>
+        <v>3.635</v>
       </c>
       <c r="G6">
         <v>2.01</v>
@@ -1779,28 +1779,28 @@
         <v>3.299</v>
       </c>
       <c r="M6">
-        <v>0.1462724</v>
+        <v>0.1828405</v>
       </c>
       <c r="N6">
-        <v>3.1527276</v>
+        <v>3.1161595</v>
       </c>
       <c r="O6">
-        <v>0.4729091400000001</v>
+        <v>0.467423925</v>
       </c>
       <c r="P6">
-        <v>2.67981846</v>
+        <v>2.648735575</v>
       </c>
       <c r="Q6">
-        <v>2.70581846</v>
+        <v>2.674735575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08544081960803421</v>
+        <v>0.08579764155727521</v>
       </c>
       <c r="T6">
-        <v>0.5456708029066138</v>
+        <v>0.5505825913474761</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.5538105616644</v>
+        <v>18.04304844933152</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08364550947941143</v>
+        <v>0.08355763213511007</v>
       </c>
       <c r="C7">
-        <v>79.11872840831194</v>
+        <v>78.57965185637467</v>
       </c>
       <c r="D7">
-        <v>80.74372840831194</v>
+        <v>80.93165185637466</v>
       </c>
       <c r="E7">
-        <v>-29.065</v>
+        <v>-28.338</v>
       </c>
       <c r="F7">
-        <v>3.635</v>
+        <v>4.362</v>
       </c>
       <c r="G7">
         <v>2.01</v>
@@ -1861,28 +1861,28 @@
         <v>3.299</v>
       </c>
       <c r="M7">
-        <v>0.1828405</v>
+        <v>0.2194086</v>
       </c>
       <c r="N7">
-        <v>3.1161595</v>
+        <v>3.0795914</v>
       </c>
       <c r="O7">
-        <v>0.467423925</v>
+        <v>0.46193871</v>
       </c>
       <c r="P7">
-        <v>2.648735575</v>
+        <v>2.61765269</v>
       </c>
       <c r="Q7">
-        <v>2.674735575</v>
+        <v>2.64365269</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08579764155727521</v>
+        <v>0.08616205546288305</v>
       </c>
       <c r="T7">
-        <v>0.5505825913474761</v>
+        <v>0.555598885925378</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.04304844933152</v>
+        <v>15.03587370777627</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08355763213511005</v>
+        <v>0.0834697547908087</v>
       </c>
       <c r="C8">
-        <v>78.5796518563747</v>
+        <v>78.04145209344962</v>
       </c>
       <c r="D8">
-        <v>80.93165185637469</v>
+        <v>81.12045209344961</v>
       </c>
       <c r="E8">
-        <v>-28.338</v>
+        <v>-27.611</v>
       </c>
       <c r="F8">
-        <v>4.362</v>
+        <v>5.089</v>
       </c>
       <c r="G8">
         <v>2.01</v>
@@ -1943,28 +1943,28 @@
         <v>3.299</v>
       </c>
       <c r="M8">
-        <v>0.2194086</v>
+        <v>0.2559766999999999</v>
       </c>
       <c r="N8">
-        <v>3.0795914</v>
+        <v>3.043023300000001</v>
       </c>
       <c r="O8">
-        <v>0.46193871</v>
+        <v>0.4564534950000001</v>
       </c>
       <c r="P8">
-        <v>2.61765269</v>
+        <v>2.586569805000001</v>
       </c>
       <c r="Q8">
-        <v>2.64365269</v>
+        <v>2.612569805000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08616205546288305</v>
+        <v>0.08653430622667602</v>
       </c>
       <c r="T8">
-        <v>0.555598885925378</v>
+        <v>0.5607230578060305</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.03587370777627</v>
+        <v>12.88789174952252</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08346975479080869</v>
+        <v>0.08348387744650733</v>
       </c>
       <c r="C9">
-        <v>78.04145209344965</v>
+        <v>77.28405086372854</v>
       </c>
       <c r="D9">
-        <v>81.12045209344964</v>
+        <v>81.09005086372854</v>
       </c>
       <c r="E9">
-        <v>-27.611</v>
+        <v>-26.884</v>
       </c>
       <c r="F9">
-        <v>5.089</v>
+        <v>5.816000000000001</v>
       </c>
       <c r="G9">
         <v>2.01</v>
@@ -2025,45 +2025,45 @@
         <v>3.299</v>
       </c>
       <c r="M9">
-        <v>0.2559767</v>
+        <v>0.3012688</v>
       </c>
       <c r="N9">
-        <v>3.0430233</v>
+        <v>2.9977312</v>
       </c>
       <c r="O9">
-        <v>0.456453495</v>
+        <v>0.4496596800000001</v>
       </c>
       <c r="P9">
-        <v>2.586569805</v>
+        <v>2.548071520000001</v>
       </c>
       <c r="Q9">
-        <v>2.612569805</v>
+        <v>2.57407152</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08653430622667602</v>
+        <v>0.08691464939837754</v>
       </c>
       <c r="T9">
-        <v>0.5607230578060305</v>
+        <v>0.5659586247275666</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.15</v>
       </c>
       <c r="W9">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>12.88789174952252</v>
+        <v>10.95035396961119</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08348387744650733</v>
+        <v>0.08353880010220593</v>
       </c>
       <c r="C10">
-        <v>77.28405086372854</v>
+        <v>76.43903754766895</v>
       </c>
       <c r="D10">
-        <v>81.09005086372854</v>
+        <v>80.97203754766895</v>
       </c>
       <c r="E10">
-        <v>-26.884</v>
+        <v>-26.157</v>
       </c>
       <c r="F10">
-        <v>5.816000000000001</v>
+        <v>6.543</v>
       </c>
       <c r="G10">
         <v>2.01</v>
@@ -2107,45 +2107,45 @@
         <v>3.299</v>
       </c>
       <c r="M10">
-        <v>0.3012688</v>
+        <v>0.3500505</v>
       </c>
       <c r="N10">
-        <v>2.9977312</v>
+        <v>2.9489495</v>
       </c>
       <c r="O10">
-        <v>0.4496596800000001</v>
+        <v>0.442342425</v>
       </c>
       <c r="P10">
-        <v>2.548071520000001</v>
+        <v>2.506607075</v>
       </c>
       <c r="Q10">
-        <v>2.57407152</v>
+        <v>2.532607075</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08691464939837754</v>
+        <v>0.08730335176066586</v>
       </c>
       <c r="T10">
-        <v>0.5659586247275666</v>
+        <v>0.5713092590539717</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.15</v>
       </c>
       <c r="W10">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.95035396961119</v>
+        <v>9.424354485995593</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08353880010220593</v>
+        <v>0.08347812275790457</v>
       </c>
       <c r="C11">
-        <v>76.43903754766895</v>
+        <v>75.84243598159921</v>
       </c>
       <c r="D11">
-        <v>80.97203754766895</v>
+        <v>81.1024359815992</v>
       </c>
       <c r="E11">
-        <v>-26.157</v>
+        <v>-25.43</v>
       </c>
       <c r="F11">
-        <v>6.543</v>
+        <v>7.27</v>
       </c>
       <c r="G11">
         <v>2.01</v>
@@ -2189,28 +2189,28 @@
         <v>3.299</v>
       </c>
       <c r="M11">
-        <v>0.3500505</v>
+        <v>0.388945</v>
       </c>
       <c r="N11">
-        <v>2.9489495</v>
+        <v>2.910055</v>
       </c>
       <c r="O11">
-        <v>0.442342425</v>
+        <v>0.43650825</v>
       </c>
       <c r="P11">
-        <v>2.506607075</v>
+        <v>2.47354675</v>
       </c>
       <c r="Q11">
-        <v>2.532607075</v>
+        <v>2.49954675</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08730335176066586</v>
+        <v>0.0877006919532273</v>
       </c>
       <c r="T11">
-        <v>0.5713092590539717</v>
+        <v>0.5767787963654082</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.424354485995593</v>
+        <v>8.481919037396034</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08347812275790457</v>
+        <v>0.08341744541360319</v>
       </c>
       <c r="C12">
-        <v>75.84243598159921</v>
+        <v>75.24625508368416</v>
       </c>
       <c r="D12">
-        <v>81.1024359815992</v>
+        <v>81.23325508368416</v>
       </c>
       <c r="E12">
-        <v>-25.43</v>
+        <v>-24.703</v>
       </c>
       <c r="F12">
-        <v>7.27</v>
+        <v>7.997000000000001</v>
       </c>
       <c r="G12">
         <v>2.01</v>
@@ -2271,28 +2271,28 @@
         <v>3.299</v>
       </c>
       <c r="M12">
-        <v>0.388945</v>
+        <v>0.4278395</v>
       </c>
       <c r="N12">
-        <v>2.910055</v>
+        <v>2.8711605</v>
       </c>
       <c r="O12">
-        <v>0.43650825</v>
+        <v>0.430674075</v>
       </c>
       <c r="P12">
-        <v>2.47354675</v>
+        <v>2.440486425</v>
       </c>
       <c r="Q12">
-        <v>2.49954675</v>
+        <v>2.466486425</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0877006919532273</v>
+        <v>0.08810696113887999</v>
       </c>
       <c r="T12">
-        <v>0.5767787963654082</v>
+        <v>0.5823712446276632</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.481919037396032</v>
+        <v>7.710835488541848</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08341744541360319</v>
+        <v>0.08343836806930181</v>
       </c>
       <c r="C13">
-        <v>75.24625508368416</v>
+        <v>74.47409862460852</v>
       </c>
       <c r="D13">
-        <v>81.23325508368416</v>
+        <v>81.18809862460851</v>
       </c>
       <c r="E13">
-        <v>-24.703</v>
+        <v>-23.976</v>
       </c>
       <c r="F13">
-        <v>7.997000000000001</v>
+        <v>8.724</v>
       </c>
       <c r="G13">
         <v>2.01</v>
@@ -2353,45 +2353,45 @@
         <v>3.299</v>
       </c>
       <c r="M13">
-        <v>0.4278395</v>
+        <v>0.4737132</v>
       </c>
       <c r="N13">
-        <v>2.8711605</v>
+        <v>2.8252868</v>
       </c>
       <c r="O13">
-        <v>0.430674075</v>
+        <v>0.42379302</v>
       </c>
       <c r="P13">
-        <v>2.440486425</v>
+        <v>2.40149378</v>
       </c>
       <c r="Q13">
-        <v>2.466486425</v>
+        <v>2.42749378</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08810696113887999</v>
+        <v>0.0885224637151157</v>
       </c>
       <c r="T13">
-        <v>0.5823712446276632</v>
+        <v>0.5880907939867879</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.710835488541848</v>
+        <v>6.964129350839285</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08343836806930181</v>
+        <v>0.08338449072500044</v>
       </c>
       <c r="C14">
-        <v>74.47409862460852</v>
+        <v>73.86348171397316</v>
       </c>
       <c r="D14">
-        <v>81.18809862460851</v>
+        <v>81.30448171397315</v>
       </c>
       <c r="E14">
-        <v>-23.976</v>
+        <v>-23.249</v>
       </c>
       <c r="F14">
-        <v>8.724</v>
+        <v>9.451000000000001</v>
       </c>
       <c r="G14">
         <v>2.01</v>
@@ -2435,28 +2435,28 @@
         <v>3.299</v>
       </c>
       <c r="M14">
-        <v>0.4737132</v>
+        <v>0.5131893000000001</v>
       </c>
       <c r="N14">
-        <v>2.8252868</v>
+        <v>2.7858107</v>
       </c>
       <c r="O14">
-        <v>0.42379302</v>
+        <v>0.417871605</v>
       </c>
       <c r="P14">
-        <v>2.40149378</v>
+        <v>2.367939095</v>
       </c>
       <c r="Q14">
-        <v>2.42749378</v>
+        <v>2.393939095</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0885224637151157</v>
+        <v>0.08894751807471316</v>
       </c>
       <c r="T14">
-        <v>0.5880907939867879</v>
+        <v>0.5939418272392256</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.964129350839285</v>
+        <v>6.428427093082416</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08338449072500044</v>
+        <v>0.08344961338069905</v>
       </c>
       <c r="C15">
-        <v>73.86348171397316</v>
+        <v>72.9958490940343</v>
       </c>
       <c r="D15">
-        <v>81.30448171397315</v>
+        <v>81.16384909403429</v>
       </c>
       <c r="E15">
-        <v>-23.249</v>
+        <v>-22.522</v>
       </c>
       <c r="F15">
-        <v>9.451000000000001</v>
+        <v>10.178</v>
       </c>
       <c r="G15">
         <v>2.01</v>
@@ -2517,45 +2517,45 @@
         <v>3.299</v>
       </c>
       <c r="M15">
-        <v>0.5131893000000001</v>
+        <v>0.5628434000000001</v>
       </c>
       <c r="N15">
-        <v>2.7858107</v>
+        <v>2.7361566</v>
       </c>
       <c r="O15">
-        <v>0.417871605</v>
+        <v>0.41042349</v>
       </c>
       <c r="P15">
-        <v>2.367939095</v>
+        <v>2.32573311</v>
       </c>
       <c r="Q15">
-        <v>2.393939095</v>
+        <v>2.35173311</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08894751807471316</v>
+        <v>0.0893824574194175</v>
       </c>
       <c r="T15">
-        <v>0.5939418272392256</v>
+        <v>0.5999289310324177</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.428427093082416</v>
+        <v>5.861310623878684</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08344961338069905</v>
+        <v>0.08340423603639767</v>
       </c>
       <c r="C16">
-        <v>72.9958490940343</v>
+        <v>72.36679018560707</v>
       </c>
       <c r="D16">
-        <v>81.16384909403429</v>
+        <v>81.26179018560707</v>
       </c>
       <c r="E16">
-        <v>-22.522</v>
+        <v>-21.795</v>
       </c>
       <c r="F16">
-        <v>10.178</v>
+        <v>10.905</v>
       </c>
       <c r="G16">
         <v>2.01</v>
@@ -2599,28 +2599,28 @@
         <v>3.299</v>
       </c>
       <c r="M16">
-        <v>0.5628434000000001</v>
+        <v>0.6030465000000002</v>
       </c>
       <c r="N16">
-        <v>2.7361566</v>
+        <v>2.6959535</v>
       </c>
       <c r="O16">
-        <v>0.41042349</v>
+        <v>0.404393025</v>
       </c>
       <c r="P16">
-        <v>2.32573311</v>
+        <v>2.291560475</v>
       </c>
       <c r="Q16">
-        <v>2.35173311</v>
+        <v>2.317560475</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0893824574194175</v>
+        <v>0.08982763063105609</v>
       </c>
       <c r="T16">
-        <v>0.5999289310324177</v>
+        <v>0.6060569078560379</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.861310623878684</v>
+        <v>5.470556582286772</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08340423603639767</v>
+        <v>0.0833588586920963</v>
       </c>
       <c r="C17">
-        <v>72.36679018560707</v>
+        <v>71.73796793541642</v>
       </c>
       <c r="D17">
-        <v>81.26179018560707</v>
+        <v>81.35996793541642</v>
       </c>
       <c r="E17">
-        <v>-21.795</v>
+        <v>-21.068</v>
       </c>
       <c r="F17">
-        <v>10.905</v>
+        <v>11.632</v>
       </c>
       <c r="G17">
         <v>2.01</v>
@@ -2681,28 +2681,28 @@
         <v>3.299</v>
       </c>
       <c r="M17">
-        <v>0.6030465</v>
+        <v>0.6432496000000001</v>
       </c>
       <c r="N17">
-        <v>2.6959535</v>
+        <v>2.655750400000001</v>
       </c>
       <c r="O17">
-        <v>0.404393025</v>
+        <v>0.3983625600000001</v>
       </c>
       <c r="P17">
-        <v>2.291560475</v>
+        <v>2.25738784</v>
       </c>
       <c r="Q17">
-        <v>2.317560475</v>
+        <v>2.28338784</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08982763063105609</v>
+        <v>0.09028340320487656</v>
       </c>
       <c r="T17">
-        <v>0.6060569078560379</v>
+        <v>0.6123307888897445</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.470556582286773</v>
+        <v>5.128646795893849</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0833588586920963</v>
+        <v>0.08331348134779493</v>
       </c>
       <c r="C18">
-        <v>71.73796793541642</v>
+        <v>71.10938320226745</v>
       </c>
       <c r="D18">
-        <v>81.35996793541642</v>
+        <v>81.45838320226746</v>
       </c>
       <c r="E18">
-        <v>-21.068</v>
+        <v>-20.341</v>
       </c>
       <c r="F18">
-        <v>11.632</v>
+        <v>12.359</v>
       </c>
       <c r="G18">
         <v>2.01</v>
@@ -2763,28 +2763,28 @@
         <v>3.299</v>
       </c>
       <c r="M18">
-        <v>0.6432496000000001</v>
+        <v>0.6834527000000001</v>
       </c>
       <c r="N18">
-        <v>2.655750400000001</v>
+        <v>2.6155473</v>
       </c>
       <c r="O18">
-        <v>0.3983625600000001</v>
+        <v>0.392332095</v>
       </c>
       <c r="P18">
-        <v>2.25738784</v>
+        <v>2.223215205</v>
       </c>
       <c r="Q18">
-        <v>2.28338784</v>
+        <v>2.249215205</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09028340320487656</v>
+        <v>0.09075015825035533</v>
       </c>
       <c r="T18">
-        <v>0.6123307888897445</v>
+        <v>0.6187558477796846</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.128646795893849</v>
+        <v>4.826961690253034</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08331348134779493</v>
+        <v>0.08326810400349355</v>
       </c>
       <c r="C19">
-        <v>71.10938320226745</v>
+        <v>70.48103684912556</v>
       </c>
       <c r="D19">
-        <v>81.45838320226746</v>
+        <v>81.55703684912555</v>
       </c>
       <c r="E19">
-        <v>-20.341</v>
+        <v>-19.614</v>
       </c>
       <c r="F19">
-        <v>12.359</v>
+        <v>13.086</v>
       </c>
       <c r="G19">
         <v>2.01</v>
@@ -2845,28 +2845,28 @@
         <v>3.299</v>
       </c>
       <c r="M19">
-        <v>0.6834527000000001</v>
+        <v>0.7236558000000002</v>
       </c>
       <c r="N19">
-        <v>2.6155473</v>
+        <v>2.5753442</v>
       </c>
       <c r="O19">
-        <v>0.392332095</v>
+        <v>0.38630163</v>
       </c>
       <c r="P19">
-        <v>2.223215205</v>
+        <v>2.18904257</v>
       </c>
       <c r="Q19">
-        <v>2.249215205</v>
+        <v>2.21504257</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09075015825035533</v>
+        <v>0.09122829756523604</v>
       </c>
       <c r="T19">
-        <v>0.6187558477796846</v>
+        <v>0.6253376154230381</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.826961690253034</v>
+        <v>4.558797151905642</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08326810400349355</v>
+        <v>0.08362647665919218</v>
       </c>
       <c r="C20">
-        <v>70.48103684912556</v>
+        <v>68.98135552990389</v>
       </c>
       <c r="D20">
-        <v>81.55703684912555</v>
+        <v>80.78435552990389</v>
       </c>
       <c r="E20">
-        <v>-19.614</v>
+        <v>-18.887</v>
       </c>
       <c r="F20">
-        <v>13.086</v>
+        <v>13.813</v>
       </c>
       <c r="G20">
         <v>2.01</v>
@@ -2927,45 +2927,45 @@
         <v>3.299</v>
       </c>
       <c r="M20">
-        <v>0.7236558000000001</v>
+        <v>0.7983914000000001</v>
       </c>
       <c r="N20">
-        <v>2.5753442</v>
+        <v>2.500608600000001</v>
       </c>
       <c r="O20">
-        <v>0.3863016300000001</v>
+        <v>0.3750912900000001</v>
       </c>
       <c r="P20">
-        <v>2.18904257</v>
+        <v>2.12551731</v>
       </c>
       <c r="Q20">
-        <v>2.21504257</v>
+        <v>2.15151731</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09122829756523604</v>
+        <v>0.09171824278912613</v>
       </c>
       <c r="T20">
-        <v>0.6253376154230381</v>
+        <v>0.6320818958477089</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.558797151905644</v>
+        <v>4.132058536702676</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08362647665919218</v>
+        <v>0.08419734931489078</v>
       </c>
       <c r="C21">
-        <v>68.98135552990389</v>
+        <v>67.05329398781529</v>
       </c>
       <c r="D21">
-        <v>80.78435552990389</v>
+        <v>79.5832939878153</v>
       </c>
       <c r="E21">
-        <v>-18.887</v>
+        <v>-18.16</v>
       </c>
       <c r="F21">
-        <v>13.813</v>
+        <v>14.54</v>
       </c>
       <c r="G21">
         <v>2.01</v>
@@ -3009,45 +3009,45 @@
         <v>3.299</v>
       </c>
       <c r="M21">
-        <v>0.7983914000000001</v>
+        <v>0.891302</v>
       </c>
       <c r="N21">
-        <v>2.500608600000001</v>
+        <v>2.407698</v>
       </c>
       <c r="O21">
-        <v>0.3750912900000001</v>
+        <v>0.3611547000000001</v>
       </c>
       <c r="P21">
-        <v>2.12551731</v>
+        <v>2.0465433</v>
       </c>
       <c r="Q21">
-        <v>2.15151731</v>
+        <v>2.0725433</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09171824278912613</v>
+        <v>0.09222043664361348</v>
       </c>
       <c r="T21">
-        <v>0.6320818958477089</v>
+        <v>0.6389947832829965</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.132058536702676</v>
+        <v>3.701326823007241</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08419734931489078</v>
+        <v>0.08420297197058942</v>
       </c>
       <c r="C22">
-        <v>67.05329398781529</v>
+        <v>66.3146420390599</v>
       </c>
       <c r="D22">
-        <v>79.5832939878153</v>
+        <v>79.5716420390599</v>
       </c>
       <c r="E22">
-        <v>-18.16</v>
+        <v>-17.433</v>
       </c>
       <c r="F22">
-        <v>14.54</v>
+        <v>15.267</v>
       </c>
       <c r="G22">
         <v>2.01</v>
@@ -3091,28 +3091,28 @@
         <v>3.299</v>
       </c>
       <c r="M22">
-        <v>0.891302</v>
+        <v>0.9358671000000001</v>
       </c>
       <c r="N22">
-        <v>2.407698</v>
+        <v>2.3631329</v>
       </c>
       <c r="O22">
-        <v>0.3611547000000001</v>
+        <v>0.354469935</v>
       </c>
       <c r="P22">
-        <v>2.0465433</v>
+        <v>2.008662965</v>
       </c>
       <c r="Q22">
-        <v>2.0725433</v>
+        <v>2.034662965</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09222043664361348</v>
+        <v>0.09273534426656889</v>
       </c>
       <c r="T22">
-        <v>0.6389947832829965</v>
+        <v>0.6460826805267725</v>
       </c>
       <c r="U22">
         <v>0.0613</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.701326823007241</v>
+        <v>3.525073164768801</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08420297197058942</v>
+        <v>0.08473219462628805</v>
       </c>
       <c r="C23">
-        <v>66.3146420390599</v>
+        <v>64.50598928039992</v>
       </c>
       <c r="D23">
-        <v>79.5716420390599</v>
+        <v>78.48998928039991</v>
       </c>
       <c r="E23">
-        <v>-17.433</v>
+        <v>-16.706</v>
       </c>
       <c r="F23">
-        <v>15.267</v>
+        <v>15.994</v>
       </c>
       <c r="G23">
         <v>2.01</v>
@@ -3173,45 +3173,45 @@
         <v>3.299</v>
       </c>
       <c r="M23">
-        <v>0.9358671</v>
+        <v>1.0252154</v>
       </c>
       <c r="N23">
-        <v>2.363132900000001</v>
+        <v>2.2737846</v>
       </c>
       <c r="O23">
-        <v>0.3544699350000001</v>
+        <v>0.34106769</v>
       </c>
       <c r="P23">
-        <v>2.008662965000001</v>
+        <v>1.93271691</v>
       </c>
       <c r="Q23">
-        <v>2.034662965</v>
+        <v>1.95871691</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09273534426656888</v>
+        <v>0.09326345464908724</v>
       </c>
       <c r="T23">
-        <v>0.6460826805267724</v>
+        <v>0.653352318725517</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.525073164768802</v>
+        <v>3.217860363783064</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08473219462628805</v>
+        <v>0.08476161728198667</v>
       </c>
       <c r="C24">
-        <v>64.50598928039992</v>
+        <v>63.7197159726809</v>
       </c>
       <c r="D24">
-        <v>78.48998928039991</v>
+        <v>78.4307159726809</v>
       </c>
       <c r="E24">
-        <v>-16.706</v>
+        <v>-15.979</v>
       </c>
       <c r="F24">
-        <v>15.994</v>
+        <v>16.721</v>
       </c>
       <c r="G24">
         <v>2.01</v>
@@ -3255,28 +3255,28 @@
         <v>3.299</v>
       </c>
       <c r="M24">
-        <v>1.0252154</v>
+        <v>1.0718161</v>
       </c>
       <c r="N24">
-        <v>2.2737846</v>
+        <v>2.2271839</v>
       </c>
       <c r="O24">
-        <v>0.34106769</v>
+        <v>0.334077585</v>
       </c>
       <c r="P24">
-        <v>1.93271691</v>
+        <v>1.893106315</v>
       </c>
       <c r="Q24">
-        <v>1.95871691</v>
+        <v>1.919106315</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09326345464908724</v>
+        <v>0.09380528218439826</v>
       </c>
       <c r="T24">
-        <v>0.653352318725517</v>
+        <v>0.6608107786956574</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.217860363783064</v>
+        <v>3.07795339144467</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08476161728198667</v>
+        <v>0.08638223993768529</v>
       </c>
       <c r="C25">
-        <v>63.7197159726809</v>
+        <v>59.86064156271328</v>
       </c>
       <c r="D25">
-        <v>78.4307159726809</v>
+        <v>75.29864156271327</v>
       </c>
       <c r="E25">
-        <v>-15.979</v>
+        <v>-15.252</v>
       </c>
       <c r="F25">
-        <v>16.721</v>
+        <v>17.448</v>
       </c>
       <c r="G25">
         <v>2.01</v>
@@ -3337,45 +3337,45 @@
         <v>3.299</v>
       </c>
       <c r="M25">
-        <v>1.0718161</v>
+        <v>1.2545112</v>
       </c>
       <c r="N25">
-        <v>2.2271839</v>
+        <v>2.0444888</v>
       </c>
       <c r="O25">
-        <v>0.334077585</v>
+        <v>0.30667332</v>
       </c>
       <c r="P25">
-        <v>1.893106315</v>
+        <v>1.73781548</v>
       </c>
       <c r="Q25">
-        <v>1.919106315</v>
+        <v>1.76381548</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09380528218439826</v>
+        <v>0.09436136833905959</v>
       </c>
       <c r="T25">
-        <v>0.6608107786956574</v>
+        <v>0.66846551392817</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.15</v>
       </c>
       <c r="W25">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.07795339144467</v>
+        <v>2.629709483661844</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08638223993768529</v>
+        <v>0.08647796259338389</v>
       </c>
       <c r="C26">
-        <v>59.86064156271328</v>
+        <v>58.95645014305126</v>
       </c>
       <c r="D26">
-        <v>75.29864156271327</v>
+        <v>75.12145014305125</v>
       </c>
       <c r="E26">
-        <v>-15.252</v>
+        <v>-14.525</v>
       </c>
       <c r="F26">
-        <v>17.448</v>
+        <v>18.175</v>
       </c>
       <c r="G26">
         <v>2.01</v>
@@ -3419,28 +3419,28 @@
         <v>3.299</v>
       </c>
       <c r="M26">
-        <v>1.2545112</v>
+        <v>1.3067825</v>
       </c>
       <c r="N26">
-        <v>2.0444888</v>
+        <v>1.9922175</v>
       </c>
       <c r="O26">
-        <v>0.30667332</v>
+        <v>0.298832625</v>
       </c>
       <c r="P26">
-        <v>1.73781548</v>
+        <v>1.693384875</v>
       </c>
       <c r="Q26">
-        <v>1.76381548</v>
+        <v>1.719384875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09436136833905959</v>
+        <v>0.0949322834578452</v>
       </c>
       <c r="T26">
-        <v>0.66846551392817</v>
+        <v>0.6763243754335495</v>
       </c>
       <c r="U26">
         <v>0.07190000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.629709483661844</v>
+        <v>2.52452110431537</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08647796259338389</v>
+        <v>0.08743558524908253</v>
       </c>
       <c r="C27">
-        <v>58.95645014305126</v>
+        <v>56.50164922094204</v>
       </c>
       <c r="D27">
-        <v>75.12145014305125</v>
+        <v>73.39364922094204</v>
       </c>
       <c r="E27">
-        <v>-14.525</v>
+        <v>-13.798</v>
       </c>
       <c r="F27">
-        <v>18.175</v>
+        <v>18.902</v>
       </c>
       <c r="G27">
         <v>2.01</v>
@@ -3501,45 +3501,45 @@
         <v>3.299</v>
       </c>
       <c r="M27">
-        <v>1.3067825</v>
+        <v>1.4327716</v>
       </c>
       <c r="N27">
-        <v>1.9922175</v>
+        <v>1.8662284</v>
       </c>
       <c r="O27">
-        <v>0.298832625</v>
+        <v>0.27993426</v>
       </c>
       <c r="P27">
-        <v>1.693384875</v>
+        <v>1.58629414</v>
       </c>
       <c r="Q27">
-        <v>1.719384875</v>
+        <v>1.61229414</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0949322834578452</v>
+        <v>0.09551862871497639</v>
       </c>
       <c r="T27">
-        <v>0.6763243754335495</v>
+        <v>0.6843956386012368</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.15</v>
       </c>
       <c r="W27">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.52452110431537</v>
+        <v>2.302530284659467</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08743558524908253</v>
+        <v>0.08756445790478115</v>
       </c>
       <c r="C28">
-        <v>56.50164922094204</v>
+        <v>55.54817831814522</v>
       </c>
       <c r="D28">
-        <v>73.39364922094204</v>
+        <v>73.16717831814522</v>
       </c>
       <c r="E28">
-        <v>-13.798</v>
+        <v>-13.071</v>
       </c>
       <c r="F28">
-        <v>18.902</v>
+        <v>19.629</v>
       </c>
       <c r="G28">
         <v>2.01</v>
@@ -3583,28 +3583,28 @@
         <v>3.299</v>
       </c>
       <c r="M28">
-        <v>1.4327716</v>
+        <v>1.4878782</v>
       </c>
       <c r="N28">
-        <v>1.8662284</v>
+        <v>1.8111218</v>
       </c>
       <c r="O28">
-        <v>0.27993426</v>
+        <v>0.27166827</v>
       </c>
       <c r="P28">
-        <v>1.58629414</v>
+        <v>1.53945353</v>
       </c>
       <c r="Q28">
-        <v>1.61229414</v>
+        <v>1.56545353</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09551862871497639</v>
+        <v>0.09612103822572761</v>
       </c>
       <c r="T28">
-        <v>0.6843956386012368</v>
+        <v>0.6926880322666689</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.302530284659467</v>
+        <v>2.217251385227635</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08756445790478115</v>
+        <v>0.08769333056047977</v>
       </c>
       <c r="C29">
-        <v>55.54817831814522</v>
+        <v>54.59610075917144</v>
       </c>
       <c r="D29">
-        <v>73.16717831814522</v>
+        <v>72.94210075917144</v>
       </c>
       <c r="E29">
-        <v>-13.071</v>
+        <v>-12.344</v>
       </c>
       <c r="F29">
-        <v>19.629</v>
+        <v>20.356</v>
       </c>
       <c r="G29">
         <v>2.01</v>
@@ -3665,28 +3665,28 @@
         <v>3.299</v>
       </c>
       <c r="M29">
-        <v>1.4878782</v>
+        <v>1.5429848</v>
       </c>
       <c r="N29">
-        <v>1.8111218</v>
+        <v>1.7560152</v>
       </c>
       <c r="O29">
-        <v>0.27166827</v>
+        <v>0.26340228</v>
       </c>
       <c r="P29">
-        <v>1.53945353</v>
+        <v>1.49261292</v>
       </c>
       <c r="Q29">
-        <v>1.56545353</v>
+        <v>1.51861292</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09612103822572761</v>
+        <v>0.0967401813339997</v>
       </c>
       <c r="T29">
-        <v>0.6926880322666689</v>
+        <v>0.7012107702005851</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.217251385227635</v>
+        <v>2.13806383575522</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08769333056047977</v>
+        <v>0.0878222032161784</v>
       </c>
       <c r="C30">
-        <v>54.59610075917144</v>
+        <v>53.64540372480339</v>
       </c>
       <c r="D30">
-        <v>72.94210075917144</v>
+        <v>72.71840372480338</v>
       </c>
       <c r="E30">
-        <v>-12.344</v>
+        <v>-11.617</v>
       </c>
       <c r="F30">
-        <v>20.356</v>
+        <v>21.083</v>
       </c>
       <c r="G30">
         <v>2.01</v>
@@ -3747,28 +3747,28 @@
         <v>3.299</v>
       </c>
       <c r="M30">
-        <v>1.5429848</v>
+        <v>1.5980914</v>
       </c>
       <c r="N30">
-        <v>1.7560152</v>
+        <v>1.7009086</v>
       </c>
       <c r="O30">
-        <v>0.26340228</v>
+        <v>0.25513629</v>
       </c>
       <c r="P30">
-        <v>1.49261292</v>
+        <v>1.44577231</v>
       </c>
       <c r="Q30">
-        <v>1.51861292</v>
+        <v>1.47177231</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0967401813339997</v>
+        <v>0.09737676509320901</v>
       </c>
       <c r="T30">
-        <v>0.7012107702005851</v>
+        <v>0.7099735852594004</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.13806383575522</v>
+        <v>2.064337496591246</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0878222032161784</v>
+        <v>0.09157207587187702</v>
       </c>
       <c r="C31">
-        <v>53.64540372480339</v>
+        <v>46.96095590318876</v>
       </c>
       <c r="D31">
-        <v>72.71840372480338</v>
+        <v>66.76095590318876</v>
       </c>
       <c r="E31">
-        <v>-11.617</v>
+        <v>-10.89</v>
       </c>
       <c r="F31">
-        <v>21.083</v>
+        <v>21.81</v>
       </c>
       <c r="G31">
         <v>2.01</v>
@@ -3829,45 +3829,45 @@
         <v>3.299</v>
       </c>
       <c r="M31">
-        <v>1.5980914</v>
+        <v>1.9629</v>
       </c>
       <c r="N31">
-        <v>1.7009086</v>
+        <v>1.336100000000001</v>
       </c>
       <c r="O31">
-        <v>0.25513629</v>
+        <v>0.2004150000000001</v>
       </c>
       <c r="P31">
-        <v>1.44577231</v>
+        <v>1.135685</v>
       </c>
       <c r="Q31">
-        <v>1.47177231</v>
+        <v>1.161685000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09737676509320901</v>
+        <v>0.09803153695982432</v>
       </c>
       <c r="T31">
-        <v>0.7099735852594004</v>
+        <v>0.7189867664627532</v>
       </c>
       <c r="U31">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.064337496591246</v>
+        <v>1.680676550002548</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09157207587187702</v>
+        <v>0.09182164852757564</v>
       </c>
       <c r="C32">
-        <v>46.96095590318876</v>
+        <v>45.87191522027508</v>
       </c>
       <c r="D32">
-        <v>66.76095590318876</v>
+        <v>66.39891522027507</v>
       </c>
       <c r="E32">
-        <v>-10.89</v>
+        <v>-10.163</v>
       </c>
       <c r="F32">
-        <v>21.81</v>
+        <v>22.537</v>
       </c>
       <c r="G32">
         <v>2.01</v>
@@ -3911,28 +3911,28 @@
         <v>3.299</v>
       </c>
       <c r="M32">
-        <v>1.9629</v>
+        <v>2.02833</v>
       </c>
       <c r="N32">
-        <v>1.336100000000001</v>
+        <v>1.27067</v>
       </c>
       <c r="O32">
-        <v>0.2004150000000001</v>
+        <v>0.1906005000000001</v>
       </c>
       <c r="P32">
-        <v>1.135685</v>
+        <v>1.0800695</v>
       </c>
       <c r="Q32">
-        <v>1.161685000000001</v>
+        <v>1.1060695</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09803153695982432</v>
+        <v>0.09870528772112412</v>
       </c>
       <c r="T32">
-        <v>0.7189867664627532</v>
+        <v>0.7282611992951887</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.680676550002548</v>
+        <v>1.62646117742182</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09182164852757564</v>
+        <v>0.09207122118327425</v>
       </c>
       <c r="C33">
-        <v>45.87191522027508</v>
+        <v>44.78678000829537</v>
       </c>
       <c r="D33">
-        <v>66.39891522027507</v>
+        <v>66.04078000829537</v>
       </c>
       <c r="E33">
-        <v>-10.163</v>
+        <v>-9.436</v>
       </c>
       <c r="F33">
-        <v>22.537</v>
+        <v>23.264</v>
       </c>
       <c r="G33">
         <v>2.01</v>
@@ -3993,28 +3993,28 @@
         <v>3.299</v>
       </c>
       <c r="M33">
-        <v>2.02833</v>
+        <v>2.09376</v>
       </c>
       <c r="N33">
-        <v>1.27067</v>
+        <v>1.20524</v>
       </c>
       <c r="O33">
-        <v>0.1906005000000001</v>
+        <v>0.180786</v>
       </c>
       <c r="P33">
-        <v>1.0800695</v>
+        <v>1.024454</v>
       </c>
       <c r="Q33">
-        <v>1.1060695</v>
+        <v>1.050454</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09870528772112412</v>
+        <v>0.09939885468128568</v>
       </c>
       <c r="T33">
-        <v>0.7282611992951887</v>
+        <v>0.7378084095638723</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.62646117742182</v>
+        <v>1.575634265627388</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09207122118327425</v>
+        <v>0.09232079383897289</v>
       </c>
       <c r="C34">
-        <v>44.78678000829537</v>
+        <v>43.70548741156691</v>
       </c>
       <c r="D34">
-        <v>66.04078000829537</v>
+        <v>65.6864874115669</v>
       </c>
       <c r="E34">
-        <v>-9.436</v>
+        <v>-8.709</v>
       </c>
       <c r="F34">
-        <v>23.264</v>
+        <v>23.991</v>
       </c>
       <c r="G34">
         <v>2.01</v>
@@ -4075,28 +4075,28 @@
         <v>3.299</v>
       </c>
       <c r="M34">
-        <v>2.09376</v>
+        <v>2.15919</v>
       </c>
       <c r="N34">
-        <v>1.20524</v>
+        <v>1.13981</v>
       </c>
       <c r="O34">
-        <v>0.180786</v>
+        <v>0.1709715</v>
       </c>
       <c r="P34">
-        <v>1.024454</v>
+        <v>0.9688385000000002</v>
       </c>
       <c r="Q34">
-        <v>1.050454</v>
+        <v>0.9948385000000002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09939885468128568</v>
+        <v>0.1001131251327954</v>
       </c>
       <c r="T34">
-        <v>0.7378084095638723</v>
+        <v>0.7476406111838599</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.575634265627388</v>
+        <v>1.527887772729589</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09232079383897289</v>
+        <v>0.109842983588804</v>
       </c>
       <c r="C35">
-        <v>43.70548741156691</v>
+        <v>25.00663426032518</v>
       </c>
       <c r="D35">
-        <v>65.6864874115669</v>
+        <v>47.71463426032518</v>
       </c>
       <c r="E35">
-        <v>-8.709</v>
+        <v>-7.981999999999999</v>
       </c>
       <c r="F35">
-        <v>23.991</v>
+        <v>24.718</v>
       </c>
       <c r="G35">
         <v>2.01</v>
@@ -4157,45 +4157,45 @@
         <v>3.299</v>
       </c>
       <c r="M35">
-        <v>2.15919</v>
+        <v>3.628602400000001</v>
       </c>
       <c r="N35">
-        <v>1.13981</v>
+        <v>-0.3296024000000006</v>
       </c>
       <c r="O35">
-        <v>0.1709715</v>
+        <v>-0.04944036000000009</v>
       </c>
       <c r="P35">
-        <v>0.9688385000000002</v>
+        <v>-0.2801620400000006</v>
       </c>
       <c r="Q35">
-        <v>0.9948385000000002</v>
+        <v>-0.2541620400000005</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1001131251327954</v>
+        <v>0.1011177630550217</v>
       </c>
       <c r="T35">
-        <v>0.7476406111838599</v>
+        <v>0.7614698303340257</v>
       </c>
       <c r="U35">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.15</v>
+        <v>0.1363748202338178</v>
       </c>
       <c r="W35">
-        <v>0.0765</v>
+        <v>0.1267801763896755</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y35">
-        <v>1.527887772729589</v>
+        <v>0.9091654682254522</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.109842983588804</v>
+        <v>0.110852983588804</v>
       </c>
       <c r="C36">
-        <v>25.00663426032518</v>
+        <v>23.53882610758087</v>
       </c>
       <c r="D36">
-        <v>47.71463426032518</v>
+        <v>46.97382610758088</v>
       </c>
       <c r="E36">
-        <v>-7.981999999999999</v>
+        <v>-7.254999999999999</v>
       </c>
       <c r="F36">
-        <v>24.718</v>
+        <v>25.445</v>
       </c>
       <c r="G36">
         <v>2.01</v>
@@ -4239,37 +4239,37 @@
         <v>3.299</v>
       </c>
       <c r="M36">
-        <v>3.628602400000001</v>
+        <v>3.735326000000001</v>
       </c>
       <c r="N36">
-        <v>-0.3296024000000006</v>
+        <v>-0.4363260000000007</v>
       </c>
       <c r="O36">
-        <v>-0.04944036000000009</v>
+        <v>-0.0654489000000001</v>
       </c>
       <c r="P36">
-        <v>-0.2801620400000006</v>
+        <v>-0.3708771000000006</v>
       </c>
       <c r="Q36">
-        <v>-0.2541620400000005</v>
+        <v>-0.3448771000000005</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1011177630550217</v>
+        <v>0.1019688055635605</v>
       </c>
       <c r="T36">
-        <v>0.7614698303340257</v>
+        <v>0.773184750800703</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1363748202338178</v>
+        <v>0.1324783967985659</v>
       </c>
       <c r="W36">
-        <v>0.1267801763896755</v>
+        <v>0.1273521713499705</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.9091654682254522</v>
+        <v>0.8831893119904393</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.110852983588804</v>
+        <v>0.111862983588804</v>
       </c>
       <c r="C37">
-        <v>23.53882610758087</v>
+        <v>22.09366955770475</v>
       </c>
       <c r="D37">
-        <v>46.97382610758088</v>
+        <v>46.25566955770476</v>
       </c>
       <c r="E37">
-        <v>-7.254999999999999</v>
+        <v>-6.527999999999999</v>
       </c>
       <c r="F37">
-        <v>25.445</v>
+        <v>26.172</v>
       </c>
       <c r="G37">
         <v>2.01</v>
@@ -4321,37 +4321,37 @@
         <v>3.299</v>
       </c>
       <c r="M37">
-        <v>3.735326000000001</v>
+        <v>3.842049600000001</v>
       </c>
       <c r="N37">
-        <v>-0.4363260000000007</v>
+        <v>-0.5430496000000007</v>
       </c>
       <c r="O37">
-        <v>-0.0654489000000001</v>
+        <v>-0.0814574400000001</v>
       </c>
       <c r="P37">
-        <v>-0.3708771000000006</v>
+        <v>-0.4615921600000006</v>
       </c>
       <c r="Q37">
-        <v>-0.3448771000000005</v>
+        <v>-0.4355921600000006</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1019688055635605</v>
+        <v>0.1028464431504912</v>
       </c>
       <c r="T37">
-        <v>0.773184750800703</v>
+        <v>0.785265762531964</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1324783967985659</v>
+        <v>0.128798441331939</v>
       </c>
       <c r="W37">
-        <v>0.1273521713499705</v>
+        <v>0.1278923888124714</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8831893119904393</v>
+        <v>0.8586562755462603</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.111862983588804</v>
+        <v>0.112872983588804</v>
       </c>
       <c r="C38">
-        <v>22.09366955770475</v>
+        <v>20.67014133197842</v>
       </c>
       <c r="D38">
-        <v>46.25566955770476</v>
+        <v>45.55914133197842</v>
       </c>
       <c r="E38">
-        <v>-6.528000000000002</v>
+        <v>-5.801000000000002</v>
       </c>
       <c r="F38">
-        <v>26.172</v>
+        <v>26.899</v>
       </c>
       <c r="G38">
         <v>2.01</v>
@@ -4403,37 +4403,37 @@
         <v>3.299</v>
       </c>
       <c r="M38">
-        <v>3.842049600000001</v>
+        <v>3.948773200000001</v>
       </c>
       <c r="N38">
-        <v>-0.5430496000000002</v>
+        <v>-0.6497732000000003</v>
       </c>
       <c r="O38">
-        <v>-0.08145744000000003</v>
+        <v>-0.09746598000000004</v>
       </c>
       <c r="P38">
-        <v>-0.4615921600000002</v>
+        <v>-0.5523072200000002</v>
       </c>
       <c r="Q38">
-        <v>-0.4355921600000002</v>
+        <v>-0.5263072200000002</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1028464431504912</v>
+        <v>0.103751942248118</v>
       </c>
       <c r="T38">
-        <v>0.785265762531964</v>
+        <v>0.7977302984451698</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1287984413319391</v>
+        <v>0.1253174023770218</v>
       </c>
       <c r="W38">
-        <v>0.1278923888124714</v>
+        <v>0.1284034053310532</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8586562755462605</v>
+        <v>0.8354493491801454</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.112872983588804</v>
+        <v>0.113882983588804</v>
       </c>
       <c r="C39">
-        <v>20.67014133197842</v>
+        <v>19.2672788723775</v>
       </c>
       <c r="D39">
-        <v>45.55914133197842</v>
+        <v>44.8832788723775</v>
       </c>
       <c r="E39">
-        <v>-5.801000000000002</v>
+        <v>-5.074000000000002</v>
       </c>
       <c r="F39">
-        <v>26.899</v>
+        <v>27.626</v>
       </c>
       <c r="G39">
         <v>2.01</v>
@@ -4485,37 +4485,37 @@
         <v>3.299</v>
       </c>
       <c r="M39">
-        <v>3.948773200000001</v>
+        <v>4.0554968</v>
       </c>
       <c r="N39">
-        <v>-0.6497732000000003</v>
+        <v>-0.7564967999999999</v>
       </c>
       <c r="O39">
-        <v>-0.09746598000000004</v>
+        <v>-0.11347452</v>
       </c>
       <c r="P39">
-        <v>-0.5523072200000002</v>
+        <v>-0.6430222799999998</v>
       </c>
       <c r="Q39">
-        <v>-0.5263072200000002</v>
+        <v>-0.6170222799999998</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.103751942248118</v>
+        <v>0.1046866509940554</v>
       </c>
       <c r="T39">
-        <v>0.7977302984451698</v>
+        <v>0.8105969161620274</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1253174023770218</v>
+        <v>0.1220195759986791</v>
       </c>
       <c r="W39">
-        <v>0.1284034053310532</v>
+        <v>0.1288875262433939</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8354493491801454</v>
+        <v>0.8134638399911942</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.113882983588804</v>
+        <v>0.1364303706384485</v>
       </c>
       <c r="C40">
-        <v>19.2672788723775</v>
+        <v>7.374036765415369</v>
       </c>
       <c r="D40">
-        <v>44.8832788723775</v>
+        <v>33.71703676541537</v>
       </c>
       <c r="E40">
-        <v>-5.074000000000002</v>
+        <v>-4.347000000000001</v>
       </c>
       <c r="F40">
-        <v>27.626</v>
+        <v>28.353</v>
       </c>
       <c r="G40">
         <v>2.01</v>
@@ -4567,45 +4567,45 @@
         <v>3.299</v>
       </c>
       <c r="M40">
-        <v>4.0554968</v>
+        <v>5.6932824</v>
       </c>
       <c r="N40">
-        <v>-0.7564967999999999</v>
+        <v>-2.3942824</v>
       </c>
       <c r="O40">
-        <v>-0.11347452</v>
+        <v>-0.3591423599999999</v>
       </c>
       <c r="P40">
-        <v>-0.6430222799999998</v>
+        <v>-2.03514004</v>
       </c>
       <c r="Q40">
-        <v>-0.6170222799999998</v>
+        <v>-2.00914004</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1046866509940554</v>
+        <v>0.1064346076491129</v>
       </c>
       <c r="T40">
-        <v>0.8105969161620274</v>
+        <v>0.8346581974584882</v>
       </c>
       <c r="U40">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1220195759986791</v>
+        <v>0.08691822488903765</v>
       </c>
       <c r="W40">
-        <v>0.1288875262433939</v>
+        <v>0.1833468204422812</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.8134638399911942</v>
+        <v>0.5794548325935844</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1364303706384485</v>
+        <v>0.1379803706384485</v>
       </c>
       <c r="C41">
-        <v>7.374036765415369</v>
+        <v>6.080089522478215</v>
       </c>
       <c r="D41">
-        <v>33.71703676541537</v>
+        <v>33.15008952247822</v>
       </c>
       <c r="E41">
-        <v>-4.347000000000001</v>
+        <v>-3.620000000000001</v>
       </c>
       <c r="F41">
-        <v>28.353</v>
+        <v>29.08</v>
       </c>
       <c r="G41">
         <v>2.01</v>
@@ -4649,37 +4649,37 @@
         <v>3.299</v>
       </c>
       <c r="M41">
-        <v>5.6932824</v>
+        <v>5.839264000000001</v>
       </c>
       <c r="N41">
-        <v>-2.3942824</v>
+        <v>-2.540264000000001</v>
       </c>
       <c r="O41">
-        <v>-0.3591423599999999</v>
+        <v>-0.3810396000000001</v>
       </c>
       <c r="P41">
-        <v>-2.03514004</v>
+        <v>-2.1592244</v>
       </c>
       <c r="Q41">
-        <v>-2.00914004</v>
+        <v>-2.1332244</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1064346076491129</v>
+        <v>0.1074451844432647</v>
       </c>
       <c r="T41">
-        <v>0.8346581974584882</v>
+        <v>0.8485691674161298</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.08691822488903765</v>
+        <v>0.08474526926681171</v>
       </c>
       <c r="W41">
-        <v>0.1833468204422812</v>
+        <v>0.1837831499312242</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5794548325935844</v>
+        <v>0.5649684617787447</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1379803706384485</v>
+        <v>0.1395303706384485</v>
       </c>
       <c r="C42">
-        <v>6.080089522478215</v>
+        <v>4.804893261118679</v>
       </c>
       <c r="D42">
-        <v>33.15008952247822</v>
+        <v>32.60189326111868</v>
       </c>
       <c r="E42">
-        <v>-3.620000000000001</v>
+        <v>-2.893000000000001</v>
       </c>
       <c r="F42">
-        <v>29.08</v>
+        <v>29.807</v>
       </c>
       <c r="G42">
         <v>2.01</v>
@@ -4731,37 +4731,37 @@
         <v>3.299</v>
       </c>
       <c r="M42">
-        <v>5.839264000000001</v>
+        <v>5.985245600000001</v>
       </c>
       <c r="N42">
-        <v>-2.540264000000001</v>
+        <v>-2.6862456</v>
       </c>
       <c r="O42">
-        <v>-0.3810396000000001</v>
+        <v>-0.40293684</v>
       </c>
       <c r="P42">
-        <v>-2.1592244</v>
+        <v>-2.28330876</v>
       </c>
       <c r="Q42">
-        <v>-2.1332244</v>
+        <v>-2.25730876</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1074451844432647</v>
+        <v>0.1084900180778963</v>
       </c>
       <c r="T42">
-        <v>0.8485691674161298</v>
+        <v>0.86295169567742</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.08474526926681171</v>
+        <v>0.08267831147981629</v>
       </c>
       <c r="W42">
-        <v>0.1837831499312242</v>
+        <v>0.1841981950548529</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5649684617787447</v>
+        <v>0.5511887431987753</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1395303706384485</v>
+        <v>0.1410803706384485</v>
       </c>
       <c r="C43">
-        <v>4.804893261118679</v>
+        <v>3.547532870871176</v>
       </c>
       <c r="D43">
-        <v>32.60189326111868</v>
+        <v>32.07153287087118</v>
       </c>
       <c r="E43">
-        <v>-2.893000000000001</v>
+        <v>-2.166</v>
       </c>
       <c r="F43">
-        <v>29.807</v>
+        <v>30.534</v>
       </c>
       <c r="G43">
         <v>2.01</v>
@@ -4813,37 +4813,37 @@
         <v>3.299</v>
       </c>
       <c r="M43">
-        <v>5.985245600000001</v>
+        <v>6.131227200000001</v>
       </c>
       <c r="N43">
-        <v>-2.6862456</v>
+        <v>-2.8322272</v>
       </c>
       <c r="O43">
-        <v>-0.40293684</v>
+        <v>-0.42483408</v>
       </c>
       <c r="P43">
-        <v>-2.28330876</v>
+        <v>-2.40739312</v>
       </c>
       <c r="Q43">
-        <v>-2.25730876</v>
+        <v>-2.38139312</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1084900180778963</v>
+        <v>0.1095708804585497</v>
       </c>
       <c r="T43">
-        <v>0.86295169567742</v>
+        <v>0.8778301731890997</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.08267831147981629</v>
+        <v>0.08070978025410638</v>
       </c>
       <c r="W43">
-        <v>0.1841981950548529</v>
+        <v>0.1845934761249755</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5511887431987753</v>
+        <v>0.5380652016940426</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1410803706384485</v>
+        <v>0.1426303706384485</v>
       </c>
       <c r="C44">
-        <v>3.54753287087118</v>
+        <v>2.307151835333652</v>
       </c>
       <c r="D44">
-        <v>32.07153287087118</v>
+        <v>31.55815183533365</v>
       </c>
       <c r="E44">
-        <v>-2.166000000000004</v>
+        <v>-1.439000000000004</v>
       </c>
       <c r="F44">
-        <v>30.534</v>
+        <v>31.261</v>
       </c>
       <c r="G44">
         <v>2.01</v>
@@ -4895,37 +4895,37 @@
         <v>3.299</v>
       </c>
       <c r="M44">
-        <v>6.1312272</v>
+        <v>6.2772088</v>
       </c>
       <c r="N44">
-        <v>-2.832227199999999</v>
+        <v>-2.9782088</v>
       </c>
       <c r="O44">
-        <v>-0.4248340799999999</v>
+        <v>-0.44673132</v>
       </c>
       <c r="P44">
-        <v>-2.407393119999999</v>
+        <v>-2.53147748</v>
       </c>
       <c r="Q44">
-        <v>-2.381393119999999</v>
+        <v>-2.50547748</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1095708804585497</v>
+        <v>0.1106896678350155</v>
       </c>
       <c r="T44">
-        <v>0.8778301731890996</v>
+        <v>0.8932307025432944</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.0807097802541064</v>
+        <v>0.07883280862028996</v>
       </c>
       <c r="W44">
-        <v>0.1845934761249755</v>
+        <v>0.1849703720290458</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5380652016940427</v>
+        <v>0.5255520574685998</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1426303706384485</v>
+        <v>0.1441803706384485</v>
       </c>
       <c r="C45">
-        <v>2.307151835333652</v>
+        <v>1.082947616368738</v>
       </c>
       <c r="D45">
-        <v>31.55815183533365</v>
+        <v>31.06094761636874</v>
       </c>
       <c r="E45">
-        <v>-1.439000000000004</v>
+        <v>-0.7119999999999997</v>
       </c>
       <c r="F45">
-        <v>31.261</v>
+        <v>31.988</v>
       </c>
       <c r="G45">
         <v>2.01</v>
@@ -4977,37 +4977,37 @@
         <v>3.299</v>
       </c>
       <c r="M45">
-        <v>6.2772088</v>
+        <v>6.423190400000001</v>
       </c>
       <c r="N45">
-        <v>-2.9782088</v>
+        <v>-3.124190400000001</v>
       </c>
       <c r="O45">
-        <v>-0.44673132</v>
+        <v>-0.4686285600000001</v>
       </c>
       <c r="P45">
-        <v>-2.53147748</v>
+        <v>-2.655561840000001</v>
       </c>
       <c r="Q45">
-        <v>-2.50547748</v>
+        <v>-2.629561840000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1106896678350155</v>
+        <v>0.1118484119034979</v>
       </c>
       <c r="T45">
-        <v>0.8932307025432944</v>
+        <v>0.9091812508029962</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.07883280862028996</v>
+        <v>0.07704115387891973</v>
       </c>
       <c r="W45">
-        <v>0.1849703720290458</v>
+        <v>0.1853301363011129</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5255520574685998</v>
+        <v>0.5136076925261315</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1441803706384485</v>
+        <v>0.1457303706384485</v>
       </c>
       <c r="C46">
-        <v>1.082947616368738</v>
+        <v>-0.1258325321264451</v>
       </c>
       <c r="D46">
-        <v>31.06094761636874</v>
+        <v>30.57916746787356</v>
       </c>
       <c r="E46">
-        <v>-0.7119999999999997</v>
+        <v>0.01500000000000057</v>
       </c>
       <c r="F46">
-        <v>31.988</v>
+        <v>32.715</v>
       </c>
       <c r="G46">
         <v>2.01</v>
@@ -5059,37 +5059,37 @@
         <v>3.299</v>
       </c>
       <c r="M46">
-        <v>6.423190400000001</v>
+        <v>6.569172000000001</v>
       </c>
       <c r="N46">
-        <v>-3.124190400000001</v>
+        <v>-3.270172000000001</v>
       </c>
       <c r="O46">
-        <v>-0.4686285600000001</v>
+        <v>-0.4905258000000001</v>
       </c>
       <c r="P46">
-        <v>-2.655561840000001</v>
+        <v>-2.779646200000001</v>
       </c>
       <c r="Q46">
-        <v>-2.629561840000001</v>
+        <v>-2.753646200000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1118484119034979</v>
+        <v>0.1130492921199251</v>
       </c>
       <c r="T46">
-        <v>0.9091812508029962</v>
+        <v>0.9257118189994141</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.07704115387891973</v>
+        <v>0.07532912823716596</v>
       </c>
       <c r="W46">
-        <v>0.1853301363011129</v>
+        <v>0.1856739110499771</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5136076925261315</v>
+        <v>0.5021941882477731</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1457303706384485</v>
+        <v>0.1635730020791762</v>
       </c>
       <c r="C47">
-        <v>-0.1258325321264451</v>
+        <v>-5.485582018521924</v>
       </c>
       <c r="D47">
-        <v>30.57916746787356</v>
+        <v>25.94641798147808</v>
       </c>
       <c r="E47">
-        <v>0.01500000000000057</v>
+        <v>0.7419999999999973</v>
       </c>
       <c r="F47">
-        <v>32.715</v>
+        <v>33.442</v>
       </c>
       <c r="G47">
         <v>2.01</v>
@@ -5141,45 +5141,45 @@
         <v>3.299</v>
       </c>
       <c r="M47">
-        <v>6.569172000000001</v>
+        <v>7.885623600000001</v>
       </c>
       <c r="N47">
-        <v>-3.270172000000001</v>
+        <v>-4.5866236</v>
       </c>
       <c r="O47">
-        <v>-0.4905258000000001</v>
+        <v>-0.68799354</v>
       </c>
       <c r="P47">
-        <v>-2.779646200000001</v>
+        <v>-3.89863006</v>
       </c>
       <c r="Q47">
-        <v>-2.753646200000001</v>
+        <v>-3.872630060000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1130492921199251</v>
+        <v>0.1146513742716417</v>
       </c>
       <c r="T47">
-        <v>0.9257118189994141</v>
+        <v>0.9477650828494968</v>
       </c>
       <c r="U47">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.07532912823716596</v>
+        <v>0.0627534390558535</v>
       </c>
       <c r="W47">
-        <v>0.1856739110499771</v>
+        <v>0.2210027390706298</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.5021941882477731</v>
+        <v>0.4183562603723566</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1635730020791762</v>
+        <v>0.1654730020791762</v>
       </c>
       <c r="C48">
-        <v>-5.485582018521924</v>
+        <v>-6.624522834815593</v>
       </c>
       <c r="D48">
-        <v>25.94641798147808</v>
+        <v>25.53447716518441</v>
       </c>
       <c r="E48">
-        <v>0.7419999999999973</v>
+        <v>1.469000000000001</v>
       </c>
       <c r="F48">
-        <v>33.442</v>
+        <v>34.169</v>
       </c>
       <c r="G48">
         <v>2.01</v>
@@ -5223,37 +5223,37 @@
         <v>3.299</v>
       </c>
       <c r="M48">
-        <v>7.885623600000001</v>
+        <v>8.057050200000001</v>
       </c>
       <c r="N48">
-        <v>-4.5866236</v>
+        <v>-4.7580502</v>
       </c>
       <c r="O48">
-        <v>-0.68799354</v>
+        <v>-0.7137075300000001</v>
       </c>
       <c r="P48">
-        <v>-3.89863006</v>
+        <v>-4.044342670000001</v>
       </c>
       <c r="Q48">
-        <v>-3.872630060000001</v>
+        <v>-4.018342670000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1146513742716417</v>
+        <v>0.1159504568050689</v>
       </c>
       <c r="T48">
-        <v>0.9477650828494968</v>
+        <v>0.9656474429032608</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0627534390558535</v>
+        <v>0.06141825950147362</v>
       </c>
       <c r="W48">
-        <v>0.2210027390706298</v>
+        <v>0.2213175744095525</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4183562603723566</v>
+        <v>0.4094550633431575</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1654730020791762</v>
+        <v>0.1673730020791762</v>
       </c>
       <c r="C49">
-        <v>-6.624522834815593</v>
+        <v>-7.750587641837903</v>
       </c>
       <c r="D49">
-        <v>25.53447716518441</v>
+        <v>25.1354123581621</v>
       </c>
       <c r="E49">
-        <v>1.469000000000001</v>
+        <v>2.195999999999998</v>
       </c>
       <c r="F49">
-        <v>34.169</v>
+        <v>34.896</v>
       </c>
       <c r="G49">
         <v>2.01</v>
@@ -5305,37 +5305,37 @@
         <v>3.299</v>
       </c>
       <c r="M49">
-        <v>8.057050200000001</v>
+        <v>8.228476800000001</v>
       </c>
       <c r="N49">
-        <v>-4.7580502</v>
+        <v>-4.929476800000001</v>
       </c>
       <c r="O49">
-        <v>-0.7137075300000001</v>
+        <v>-0.7394215200000001</v>
       </c>
       <c r="P49">
-        <v>-4.044342670000001</v>
+        <v>-4.190055280000001</v>
       </c>
       <c r="Q49">
-        <v>-4.018342670000001</v>
+        <v>-4.164055280000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1159504568050689</v>
+        <v>0.1172995040513202</v>
       </c>
       <c r="T49">
-        <v>0.9656474429032608</v>
+        <v>0.9842175860360157</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06141825950147362</v>
+        <v>0.06013871242852626</v>
       </c>
       <c r="W49">
-        <v>0.2213175744095525</v>
+        <v>0.2216192916093535</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4094550633431575</v>
+        <v>0.4009247495235084</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1673730020791762</v>
+        <v>0.1692730020791762</v>
       </c>
       <c r="C50">
-        <v>-7.750587641837903</v>
+        <v>-8.864370846881251</v>
       </c>
       <c r="D50">
-        <v>25.1354123581621</v>
+        <v>24.74862915311875</v>
       </c>
       <c r="E50">
-        <v>2.195999999999998</v>
+        <v>2.922999999999995</v>
       </c>
       <c r="F50">
-        <v>34.896</v>
+        <v>35.623</v>
       </c>
       <c r="G50">
         <v>2.01</v>
@@ -5387,37 +5387,37 @@
         <v>3.299</v>
       </c>
       <c r="M50">
-        <v>8.228476800000001</v>
+        <v>8.399903399999999</v>
       </c>
       <c r="N50">
-        <v>-4.929476800000001</v>
+        <v>-5.100903399999999</v>
       </c>
       <c r="O50">
-        <v>-0.7394215200000001</v>
+        <v>-0.7651355099999998</v>
       </c>
       <c r="P50">
-        <v>-4.190055280000001</v>
+        <v>-4.33576789</v>
       </c>
       <c r="Q50">
-        <v>-4.164055280000001</v>
+        <v>-4.30976789</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1172995040513202</v>
+        <v>0.11870145511115</v>
       </c>
       <c r="T50">
-        <v>0.9842175860360157</v>
+        <v>1.003515970075938</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06013871242852626</v>
+        <v>0.05891139176671961</v>
       </c>
       <c r="W50">
-        <v>0.2216192916093535</v>
+        <v>0.2219086938214075</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4009247495235084</v>
+        <v>0.3927426117781307</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1692730020791762</v>
+        <v>0.1711730020791762</v>
       </c>
       <c r="C51">
-        <v>-8.864370846881251</v>
+        <v>-9.966430824796035</v>
       </c>
       <c r="D51">
-        <v>24.74862915311875</v>
+        <v>24.37356917520396</v>
       </c>
       <c r="E51">
-        <v>2.922999999999995</v>
+        <v>3.649999999999999</v>
       </c>
       <c r="F51">
-        <v>35.623</v>
+        <v>36.35</v>
       </c>
       <c r="G51">
         <v>2.01</v>
@@ -5469,37 +5469,37 @@
         <v>3.299</v>
       </c>
       <c r="M51">
-        <v>8.399903399999999</v>
+        <v>8.571330000000001</v>
       </c>
       <c r="N51">
-        <v>-5.100903399999999</v>
+        <v>-5.272330000000001</v>
       </c>
       <c r="O51">
-        <v>-0.7651355099999998</v>
+        <v>-0.7908495000000001</v>
       </c>
       <c r="P51">
-        <v>-4.33576789</v>
+        <v>-4.481480500000001</v>
       </c>
       <c r="Q51">
-        <v>-4.30976789</v>
+        <v>-4.455480500000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.11870145511115</v>
+        <v>0.120159484213373</v>
       </c>
       <c r="T51">
-        <v>1.003515970075938</v>
+        <v>1.023586289477456</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05891139176671961</v>
+        <v>0.0577331639313852</v>
       </c>
       <c r="W51">
-        <v>0.2219086938214075</v>
+        <v>0.2221865199449794</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3927426117781307</v>
+        <v>0.384887759542568</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1711730020791762</v>
+        <v>0.1730730020791762</v>
       </c>
       <c r="C52">
-        <v>-9.966430824796035</v>
+        <v>-11.05729260754929</v>
       </c>
       <c r="D52">
-        <v>24.37356917520396</v>
+        <v>24.00970739245071</v>
       </c>
       <c r="E52">
-        <v>3.649999999999999</v>
+        <v>4.377000000000002</v>
       </c>
       <c r="F52">
-        <v>36.35</v>
+        <v>37.07700000000001</v>
       </c>
       <c r="G52">
         <v>2.01</v>
@@ -5551,37 +5551,37 @@
         <v>3.299</v>
       </c>
       <c r="M52">
-        <v>8.571330000000001</v>
+        <v>8.742756600000002</v>
       </c>
       <c r="N52">
-        <v>-5.272330000000001</v>
+        <v>-5.443756600000001</v>
       </c>
       <c r="O52">
-        <v>-0.7908495000000001</v>
+        <v>-0.8165634900000002</v>
       </c>
       <c r="P52">
-        <v>-4.481480500000001</v>
+        <v>-4.627193110000001</v>
       </c>
       <c r="Q52">
-        <v>-4.455480500000001</v>
+        <v>-4.601193110000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.120159484213373</v>
+        <v>0.1216770247075235</v>
       </c>
       <c r="T52">
-        <v>1.023586289477456</v>
+        <v>1.044475805589241</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0577331639313852</v>
+        <v>0.05660114110920118</v>
       </c>
       <c r="W52">
-        <v>0.2221865199449794</v>
+        <v>0.2224534509264504</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.384887759542568</v>
+        <v>0.3773409407280078</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1730730020791762</v>
+        <v>0.1749730020791762</v>
       </c>
       <c r="C53">
-        <v>-11.05729260754929</v>
+        <v>-12.13745033641971</v>
       </c>
       <c r="D53">
-        <v>24.00970739245071</v>
+        <v>23.65654966358029</v>
       </c>
       <c r="E53">
-        <v>4.377000000000002</v>
+        <v>5.103999999999999</v>
       </c>
       <c r="F53">
-        <v>37.07700000000001</v>
+        <v>37.804</v>
       </c>
       <c r="G53">
         <v>2.01</v>
@@ -5633,37 +5633,37 @@
         <v>3.299</v>
       </c>
       <c r="M53">
-        <v>8.742756600000002</v>
+        <v>8.9141832</v>
       </c>
       <c r="N53">
-        <v>-5.443756600000001</v>
+        <v>-5.6151832</v>
       </c>
       <c r="O53">
-        <v>-0.8165634900000002</v>
+        <v>-0.8422774799999999</v>
       </c>
       <c r="P53">
-        <v>-4.627193110000001</v>
+        <v>-4.77290572</v>
       </c>
       <c r="Q53">
-        <v>-4.601193110000001</v>
+        <v>-4.74690572</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1216770247075235</v>
+        <v>0.1232577960555969</v>
       </c>
       <c r="T53">
-        <v>1.044475805589241</v>
+        <v>1.066235718205684</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05660114110920118</v>
+        <v>0.05551265762633194</v>
       </c>
       <c r="W53">
-        <v>0.2224534509264504</v>
+        <v>0.2227101153317109</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3773409407280078</v>
+        <v>0.3700843841755462</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1749730020791762</v>
+        <v>0.1768730020791762</v>
       </c>
       <c r="C54">
-        <v>-12.13745033641971</v>
+        <v>-13.20736950091441</v>
       </c>
       <c r="D54">
-        <v>23.65654966358029</v>
+        <v>23.3136304990856</v>
       </c>
       <c r="E54">
-        <v>5.103999999999999</v>
+        <v>5.831000000000003</v>
       </c>
       <c r="F54">
-        <v>37.804</v>
+        <v>38.53100000000001</v>
       </c>
       <c r="G54">
         <v>2.01</v>
@@ -5715,37 +5715,37 @@
         <v>3.299</v>
       </c>
       <c r="M54">
-        <v>8.9141832</v>
+        <v>9.085609800000002</v>
       </c>
       <c r="N54">
-        <v>-5.6151832</v>
+        <v>-5.786609800000002</v>
       </c>
       <c r="O54">
-        <v>-0.8422774799999999</v>
+        <v>-0.8679914700000002</v>
       </c>
       <c r="P54">
-        <v>-4.77290572</v>
+        <v>-4.918618330000001</v>
       </c>
       <c r="Q54">
-        <v>-4.74690572</v>
+        <v>-4.892618330000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1232577960555969</v>
+        <v>0.1249058342695457</v>
       </c>
       <c r="T54">
-        <v>1.066235718205684</v>
+        <v>1.088921584550486</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05551265762633194</v>
+        <v>0.05446524899187283</v>
       </c>
       <c r="W54">
-        <v>0.2227101153317109</v>
+        <v>0.2229570942877164</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3700843841755462</v>
+        <v>0.3631016599458189</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1768730020791762</v>
+        <v>0.1787730020791762</v>
       </c>
       <c r="C55">
-        <v>-13.20736950091441</v>
+        <v>-14.26748898573951</v>
       </c>
       <c r="D55">
-        <v>23.3136304990856</v>
+        <v>22.98051101426049</v>
       </c>
       <c r="E55">
-        <v>5.831000000000003</v>
+        <v>6.558</v>
       </c>
       <c r="F55">
-        <v>38.53100000000001</v>
+        <v>39.258</v>
       </c>
       <c r="G55">
         <v>2.01</v>
@@ -5797,37 +5797,37 @@
         <v>3.299</v>
       </c>
       <c r="M55">
-        <v>9.085609800000002</v>
+        <v>9.2570364</v>
       </c>
       <c r="N55">
-        <v>-5.786609800000002</v>
+        <v>-5.9580364</v>
       </c>
       <c r="O55">
-        <v>-0.8679914700000002</v>
+        <v>-0.89370546</v>
       </c>
       <c r="P55">
-        <v>-4.918618330000001</v>
+        <v>-5.064330940000001</v>
       </c>
       <c r="Q55">
-        <v>-4.892618330000001</v>
+        <v>-5.038330940000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1249058342695457</v>
+        <v>0.1266255263188837</v>
       </c>
       <c r="T55">
-        <v>1.088921584550486</v>
+        <v>1.112593792910279</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05446524899187283</v>
+        <v>0.05345663326980112</v>
       </c>
       <c r="W55">
-        <v>0.2229570942877164</v>
+        <v>0.2231949258749809</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3631016599458189</v>
+        <v>0.3563775551320075</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1787730020791762</v>
+        <v>0.1806730020791762</v>
       </c>
       <c r="C56">
-        <v>-14.26748898573951</v>
+        <v>-15.31822294475278</v>
       </c>
       <c r="D56">
-        <v>22.98051101426049</v>
+        <v>22.65677705524723</v>
       </c>
       <c r="E56">
-        <v>6.558</v>
+        <v>7.285000000000004</v>
       </c>
       <c r="F56">
-        <v>39.258</v>
+        <v>39.98500000000001</v>
       </c>
       <c r="G56">
         <v>2.01</v>
@@ -5879,37 +5879,37 @@
         <v>3.299</v>
       </c>
       <c r="M56">
-        <v>9.2570364</v>
+        <v>9.428463000000002</v>
       </c>
       <c r="N56">
-        <v>-5.9580364</v>
+        <v>-6.129463000000002</v>
       </c>
       <c r="O56">
-        <v>-0.89370546</v>
+        <v>-0.9194194500000002</v>
       </c>
       <c r="P56">
-        <v>-5.064330940000001</v>
+        <v>-5.210043550000002</v>
       </c>
       <c r="Q56">
-        <v>-5.038330940000001</v>
+        <v>-5.184043550000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1266255263188837</v>
+        <v>0.12842164912597</v>
       </c>
       <c r="T56">
-        <v>1.112593792910279</v>
+        <v>1.137318099419396</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05345663326980112</v>
+        <v>0.05248469448307745</v>
       </c>
       <c r="W56">
-        <v>0.2231949258749809</v>
+        <v>0.2234241090408904</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3563775551320075</v>
+        <v>0.3498979632205164</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1806730020791762</v>
+        <v>0.1825730020791762</v>
       </c>
       <c r="C57">
-        <v>-15.31822294475278</v>
+        <v>-16.35996251872257</v>
       </c>
       <c r="D57">
-        <v>22.65677705524723</v>
+        <v>22.34203748127743</v>
       </c>
       <c r="E57">
-        <v>7.285000000000004</v>
+        <v>8.012</v>
       </c>
       <c r="F57">
-        <v>39.98500000000001</v>
+        <v>40.712</v>
       </c>
       <c r="G57">
         <v>2.01</v>
@@ -5961,37 +5961,37 @@
         <v>3.299</v>
       </c>
       <c r="M57">
-        <v>9.428463000000002</v>
+        <v>9.599889600000001</v>
       </c>
       <c r="N57">
-        <v>-6.129463000000002</v>
+        <v>-6.300889600000001</v>
       </c>
       <c r="O57">
-        <v>-0.9194194500000002</v>
+        <v>-0.94513344</v>
       </c>
       <c r="P57">
-        <v>-5.210043550000002</v>
+        <v>-5.35575616</v>
       </c>
       <c r="Q57">
-        <v>-5.184043550000002</v>
+        <v>-5.329756160000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.12842164912597</v>
+        <v>0.130299413878833</v>
       </c>
       <c r="T57">
-        <v>1.137318099419396</v>
+        <v>1.163166238042564</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05248469448307745</v>
+        <v>0.05154746779587965</v>
       </c>
       <c r="W57">
-        <v>0.2234241090408904</v>
+        <v>0.2236451070937316</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3498979632205164</v>
+        <v>0.3436497853058643</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1825730020791762</v>
+        <v>0.1844730020791762</v>
       </c>
       <c r="C58">
-        <v>-16.35996251872257</v>
+        <v>-17.3930774118738</v>
       </c>
       <c r="D58">
-        <v>22.34203748127743</v>
+        <v>22.03592258812621</v>
       </c>
       <c r="E58">
-        <v>8.012</v>
+        <v>8.739000000000004</v>
       </c>
       <c r="F58">
-        <v>40.712</v>
+        <v>41.43900000000001</v>
       </c>
       <c r="G58">
         <v>2.01</v>
@@ -6043,37 +6043,37 @@
         <v>3.299</v>
       </c>
       <c r="M58">
-        <v>9.599889600000001</v>
+        <v>9.771316200000003</v>
       </c>
       <c r="N58">
-        <v>-6.300889600000001</v>
+        <v>-6.472316200000003</v>
       </c>
       <c r="O58">
-        <v>-0.94513344</v>
+        <v>-0.9708474300000003</v>
       </c>
       <c r="P58">
-        <v>-5.35575616</v>
+        <v>-5.501468770000002</v>
       </c>
       <c r="Q58">
-        <v>-5.329756160000001</v>
+        <v>-5.475468770000003</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.130299413878833</v>
+        <v>0.1322645165271779</v>
       </c>
       <c r="T58">
-        <v>1.163166238042564</v>
+        <v>1.190216615671461</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05154746779587965</v>
+        <v>0.05064312625560105</v>
       </c>
       <c r="W58">
-        <v>0.2236451070937316</v>
+        <v>0.2238583508289293</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3436497853058643</v>
+        <v>0.337620841704007</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1844730020791762</v>
+        <v>0.1863730020791762</v>
       </c>
       <c r="C59">
-        <v>-17.3930774118738</v>
+        <v>-18.41791734058115</v>
       </c>
       <c r="D59">
-        <v>22.03592258812621</v>
+        <v>21.73808265941886</v>
       </c>
       <c r="E59">
-        <v>8.739000000000004</v>
+        <v>9.466000000000001</v>
       </c>
       <c r="F59">
-        <v>41.43900000000001</v>
+        <v>42.166</v>
       </c>
       <c r="G59">
         <v>2.01</v>
@@ -6125,37 +6125,37 @@
         <v>3.299</v>
       </c>
       <c r="M59">
-        <v>9.771316200000003</v>
+        <v>9.942742800000001</v>
       </c>
       <c r="N59">
-        <v>-6.472316200000003</v>
+        <v>-6.643742800000001</v>
       </c>
       <c r="O59">
-        <v>-0.9708474300000003</v>
+        <v>-0.9965614200000001</v>
       </c>
       <c r="P59">
-        <v>-5.501468770000002</v>
+        <v>-5.647181380000001</v>
       </c>
       <c r="Q59">
-        <v>-5.475468770000003</v>
+        <v>-5.621181380000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1322645165271779</v>
+        <v>0.1343231954921107</v>
       </c>
       <c r="T59">
-        <v>1.190216615671461</v>
+        <v>1.218555106520782</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05064312625560105</v>
+        <v>0.04976996890636656</v>
       </c>
       <c r="W59">
-        <v>0.2238583508289293</v>
+        <v>0.2240642413318788</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.337620841704007</v>
+        <v>0.3317997927091104</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1863730020791762</v>
+        <v>0.1882730020791762</v>
       </c>
       <c r="C60">
-        <v>-18.41791734058113</v>
+        <v>-19.43481336614494</v>
       </c>
       <c r="D60">
-        <v>21.73808265941886</v>
+        <v>21.44818663385507</v>
       </c>
       <c r="E60">
-        <v>9.465999999999994</v>
+        <v>10.193</v>
       </c>
       <c r="F60">
-        <v>42.166</v>
+        <v>42.893</v>
       </c>
       <c r="G60">
         <v>2.01</v>
@@ -6207,37 +6207,37 @@
         <v>3.299</v>
       </c>
       <c r="M60">
-        <v>9.9427428</v>
+        <v>10.1141694</v>
       </c>
       <c r="N60">
-        <v>-6.643742799999999</v>
+        <v>-6.815169399999999</v>
       </c>
       <c r="O60">
-        <v>-0.9965614199999998</v>
+        <v>-1.02227541</v>
       </c>
       <c r="P60">
-        <v>-5.647181379999999</v>
+        <v>-5.79289399</v>
       </c>
       <c r="Q60">
-        <v>-5.621181379999999</v>
+        <v>-5.76689399</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1343231954921107</v>
+        <v>0.1364822978211866</v>
       </c>
       <c r="T60">
-        <v>1.218555106520781</v>
+        <v>1.248275962777386</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04976996890636657</v>
+        <v>0.0489264101113434</v>
       </c>
       <c r="W60">
-        <v>0.2240642413318788</v>
+        <v>0.2242631524957452</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3317997927091104</v>
+        <v>0.326176067408956</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1882730020791762</v>
+        <v>0.1901730020791762</v>
       </c>
       <c r="C61">
-        <v>-19.43481336614494</v>
+        <v>-20.44407912232818</v>
       </c>
       <c r="D61">
-        <v>21.44818663385507</v>
+        <v>21.16592087767181</v>
       </c>
       <c r="E61">
-        <v>10.193</v>
+        <v>10.91999999999999</v>
       </c>
       <c r="F61">
-        <v>42.893</v>
+        <v>43.62</v>
       </c>
       <c r="G61">
         <v>2.01</v>
@@ -6289,37 +6289,37 @@
         <v>3.299</v>
       </c>
       <c r="M61">
-        <v>10.1141694</v>
+        <v>10.285596</v>
       </c>
       <c r="N61">
-        <v>-6.815169399999999</v>
+        <v>-6.986596</v>
       </c>
       <c r="O61">
-        <v>-1.02227541</v>
+        <v>-1.0479894</v>
       </c>
       <c r="P61">
-        <v>-5.79289399</v>
+        <v>-5.9386066</v>
       </c>
       <c r="Q61">
-        <v>-5.76689399</v>
+        <v>-5.9126066</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1364822978211866</v>
+        <v>0.1387493552667163</v>
       </c>
       <c r="T61">
-        <v>1.248275962777386</v>
+        <v>1.27948286184682</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.0489264101113434</v>
+        <v>0.04811096994282101</v>
       </c>
       <c r="W61">
-        <v>0.2242631524957452</v>
+        <v>0.2244554332874828</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.326176067408956</v>
+        <v>0.3207397996188067</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1901730020791762</v>
+        <v>0.1920730020791762</v>
       </c>
       <c r="C62">
-        <v>-20.44407912232818</v>
+        <v>-21.44601194722371</v>
       </c>
       <c r="D62">
-        <v>21.16592087767181</v>
+        <v>20.89098805277629</v>
       </c>
       <c r="E62">
-        <v>10.91999999999999</v>
+        <v>11.647</v>
       </c>
       <c r="F62">
-        <v>43.62</v>
+        <v>44.347</v>
       </c>
       <c r="G62">
         <v>2.01</v>
@@ -6371,37 +6371,37 @@
         <v>3.299</v>
       </c>
       <c r="M62">
-        <v>10.285596</v>
+        <v>10.4570226</v>
       </c>
       <c r="N62">
-        <v>-6.986596</v>
+        <v>-7.1580226</v>
       </c>
       <c r="O62">
-        <v>-1.0479894</v>
+        <v>-1.07370339</v>
       </c>
       <c r="P62">
-        <v>-5.9386066</v>
+        <v>-6.08431921</v>
       </c>
       <c r="Q62">
-        <v>-5.9126066</v>
+        <v>-6.058319210000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1387493552667163</v>
+        <v>0.1411326720684269</v>
       </c>
       <c r="T62">
-        <v>1.27948286184682</v>
+        <v>1.312290114714688</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04811096994282101</v>
+        <v>0.04732226551752887</v>
       </c>
       <c r="W62">
-        <v>0.2244554332874828</v>
+        <v>0.2246414097909667</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3207397996188067</v>
+        <v>0.3154817701168591</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1920730020791762</v>
+        <v>0.1939730020791762</v>
       </c>
       <c r="C63">
-        <v>-21.44601194722371</v>
+        <v>-22.4408939280387</v>
       </c>
       <c r="D63">
-        <v>20.89098805277629</v>
+        <v>20.6231060719613</v>
       </c>
       <c r="E63">
-        <v>11.647</v>
+        <v>12.374</v>
       </c>
       <c r="F63">
-        <v>44.347</v>
+        <v>45.074</v>
       </c>
       <c r="G63">
         <v>2.01</v>
@@ -6453,37 +6453,37 @@
         <v>3.299</v>
       </c>
       <c r="M63">
-        <v>10.4570226</v>
+        <v>10.6284492</v>
       </c>
       <c r="N63">
-        <v>-7.1580226</v>
+        <v>-7.3294492</v>
       </c>
       <c r="O63">
-        <v>-1.07370339</v>
+        <v>-1.09941738</v>
       </c>
       <c r="P63">
-        <v>-6.08431921</v>
+        <v>-6.23003182</v>
       </c>
       <c r="Q63">
-        <v>-6.058319210000001</v>
+        <v>-6.20403182</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1411326720684269</v>
+        <v>0.1436414265965434</v>
       </c>
       <c r="T63">
-        <v>1.312290114714688</v>
+        <v>1.346824065101916</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04732226551752887</v>
+        <v>0.04655900317047194</v>
       </c>
       <c r="W63">
-        <v>0.2246414097909667</v>
+        <v>0.2248213870524027</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3154817701168591</v>
+        <v>0.310393354469813</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1939730020791762</v>
+        <v>0.1958730020791762</v>
       </c>
       <c r="C64">
-        <v>-22.4408939280387</v>
+        <v>-23.42899286651436</v>
       </c>
       <c r="D64">
-        <v>20.6231060719613</v>
+        <v>20.36200713348564</v>
       </c>
       <c r="E64">
-        <v>12.374</v>
+        <v>13.101</v>
       </c>
       <c r="F64">
-        <v>45.074</v>
+        <v>45.801</v>
       </c>
       <c r="G64">
         <v>2.01</v>
@@ -6535,37 +6535,37 @@
         <v>3.299</v>
       </c>
       <c r="M64">
-        <v>10.6284492</v>
+        <v>10.7998758</v>
       </c>
       <c r="N64">
-        <v>-7.3294492</v>
+        <v>-7.5008758</v>
       </c>
       <c r="O64">
-        <v>-1.09941738</v>
+        <v>-1.12513137</v>
       </c>
       <c r="P64">
-        <v>-6.23003182</v>
+        <v>-6.37574443</v>
       </c>
       <c r="Q64">
-        <v>-6.20403182</v>
+        <v>-6.34974443</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1436414265965434</v>
+        <v>0.1462857894775311</v>
       </c>
       <c r="T64">
-        <v>1.346824065101916</v>
+        <v>1.383224715510076</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04655900317047194</v>
+        <v>0.04581997137411525</v>
       </c>
       <c r="W64">
-        <v>0.2248213870524027</v>
+        <v>0.2249956507499836</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.310393354469813</v>
+        <v>0.305466475827435</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1958730020791762</v>
+        <v>0.1977730020791762</v>
       </c>
       <c r="C65">
-        <v>-23.42899286651436</v>
+        <v>-24.41056317192602</v>
       </c>
       <c r="D65">
-        <v>20.36200713348564</v>
+        <v>20.10743682807399</v>
       </c>
       <c r="E65">
-        <v>13.101</v>
+        <v>13.828</v>
       </c>
       <c r="F65">
-        <v>45.801</v>
+        <v>46.52800000000001</v>
       </c>
       <c r="G65">
         <v>2.01</v>
@@ -6617,37 +6617,37 @@
         <v>3.299</v>
       </c>
       <c r="M65">
-        <v>10.7998758</v>
+        <v>10.9713024</v>
       </c>
       <c r="N65">
-        <v>-7.5008758</v>
+        <v>-7.672302400000002</v>
       </c>
       <c r="O65">
-        <v>-1.12513137</v>
+        <v>-1.15084536</v>
       </c>
       <c r="P65">
-        <v>-6.37574443</v>
+        <v>-6.521457040000001</v>
       </c>
       <c r="Q65">
-        <v>-6.34974443</v>
+        <v>-6.495457040000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1462857894775311</v>
+        <v>0.1490770614074625</v>
       </c>
       <c r="T65">
-        <v>1.383224715510076</v>
+        <v>1.421647624274245</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04581997137411525</v>
+        <v>0.04510403432139469</v>
       </c>
       <c r="W65">
-        <v>0.2249956507499836</v>
+        <v>0.2251644687070151</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.305466475827435</v>
+        <v>0.3006935621426313</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1977730020791762</v>
+        <v>0.1996730020791762</v>
       </c>
       <c r="C66">
-        <v>-24.41056317192602</v>
+        <v>-25.38584668792373</v>
       </c>
       <c r="D66">
-        <v>20.10743682807399</v>
+        <v>19.85915331207627</v>
       </c>
       <c r="E66">
-        <v>13.828</v>
+        <v>14.555</v>
       </c>
       <c r="F66">
-        <v>46.52800000000001</v>
+        <v>47.255</v>
       </c>
       <c r="G66">
         <v>2.01</v>
@@ -6699,37 +6699,37 @@
         <v>3.299</v>
       </c>
       <c r="M66">
-        <v>10.9713024</v>
+        <v>11.142729</v>
       </c>
       <c r="N66">
-        <v>-7.672302400000002</v>
+        <v>-7.843729000000001</v>
       </c>
       <c r="O66">
-        <v>-1.15084536</v>
+        <v>-1.17655935</v>
       </c>
       <c r="P66">
-        <v>-6.521457040000001</v>
+        <v>-6.667169650000001</v>
       </c>
       <c r="Q66">
-        <v>-6.495457040000002</v>
+        <v>-6.641169650000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1490770614074625</v>
+        <v>0.1520278345905329</v>
       </c>
       <c r="T66">
-        <v>1.421647624274245</v>
+        <v>1.462266127824938</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04510403432139469</v>
+        <v>0.04441012610106555</v>
       </c>
       <c r="W66">
-        <v>0.2251644687070151</v>
+        <v>0.2253280922653688</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3006935621426313</v>
+        <v>0.296067507340437</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1996730020791762</v>
+        <v>0.2015730020791762</v>
       </c>
       <c r="C67">
-        <v>-25.38584668792373</v>
+        <v>-26.35507345886166</v>
       </c>
       <c r="D67">
-        <v>19.85915331207627</v>
+        <v>19.61692654113835</v>
       </c>
       <c r="E67">
-        <v>14.555</v>
+        <v>15.282</v>
       </c>
       <c r="F67">
-        <v>47.255</v>
+        <v>47.98200000000001</v>
       </c>
       <c r="G67">
         <v>2.01</v>
@@ -6781,37 +6781,37 @@
         <v>3.299</v>
       </c>
       <c r="M67">
-        <v>11.142729</v>
+        <v>11.3141556</v>
       </c>
       <c r="N67">
-        <v>-7.843729000000001</v>
+        <v>-8.0151556</v>
       </c>
       <c r="O67">
-        <v>-1.17655935</v>
+        <v>-1.20227334</v>
       </c>
       <c r="P67">
-        <v>-6.667169650000001</v>
+        <v>-6.81288226</v>
       </c>
       <c r="Q67">
-        <v>-6.641169650000001</v>
+        <v>-6.78688226</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1520278345905329</v>
+        <v>0.155152182666725</v>
       </c>
       <c r="T67">
-        <v>1.462266127824938</v>
+        <v>1.505273955113906</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04441012610106555</v>
+        <v>0.04373724540256455</v>
       </c>
       <c r="W67">
-        <v>0.2253280922653688</v>
+        <v>0.2254867575340753</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.296067507340437</v>
+        <v>0.2915816360170971</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2015730020791762</v>
+        <v>0.2034730020791762</v>
       </c>
       <c r="C68">
-        <v>-26.35507345886166</v>
+        <v>-27.31846244072074</v>
       </c>
       <c r="D68">
-        <v>19.61692654113835</v>
+        <v>19.38053755927926</v>
       </c>
       <c r="E68">
-        <v>15.282</v>
+        <v>16.009</v>
       </c>
       <c r="F68">
-        <v>47.98200000000001</v>
+        <v>48.709</v>
       </c>
       <c r="G68">
         <v>2.01</v>
@@ -6863,37 +6863,37 @@
         <v>3.299</v>
       </c>
       <c r="M68">
-        <v>11.3141556</v>
+        <v>11.4855822</v>
       </c>
       <c r="N68">
-        <v>-8.0151556</v>
+        <v>-8.1865822</v>
       </c>
       <c r="O68">
-        <v>-1.20227334</v>
+        <v>-1.22798733</v>
       </c>
       <c r="P68">
-        <v>-6.81288226</v>
+        <v>-6.958594870000001</v>
       </c>
       <c r="Q68">
-        <v>-6.78688226</v>
+        <v>-6.932594870000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.155152182666725</v>
+        <v>0.1584658851717773</v>
       </c>
       <c r="T68">
-        <v>1.505273955113906</v>
+        <v>1.550888317390086</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04373724540256455</v>
+        <v>0.04308445069506359</v>
       </c>
       <c r="W68">
-        <v>0.2254867575340753</v>
+        <v>0.225640686526104</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2915816360170971</v>
+        <v>0.287229671300424</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2034730020791762</v>
+        <v>0.2053730020791762</v>
       </c>
       <c r="C69">
-        <v>-27.31846244072074</v>
+        <v>-28.27622216124264</v>
       </c>
       <c r="D69">
-        <v>19.38053755927926</v>
+        <v>19.14977783875736</v>
       </c>
       <c r="E69">
-        <v>16.009</v>
+        <v>16.736</v>
       </c>
       <c r="F69">
-        <v>48.709</v>
+        <v>49.43600000000001</v>
       </c>
       <c r="G69">
         <v>2.01</v>
@@ -6945,37 +6945,37 @@
         <v>3.299</v>
       </c>
       <c r="M69">
-        <v>11.4855822</v>
+        <v>11.6570088</v>
       </c>
       <c r="N69">
-        <v>-8.1865822</v>
+        <v>-8.3580088</v>
       </c>
       <c r="O69">
-        <v>-1.22798733</v>
+        <v>-1.25370132</v>
       </c>
       <c r="P69">
-        <v>-6.958594870000001</v>
+        <v>-7.10430748</v>
       </c>
       <c r="Q69">
-        <v>-6.932594870000001</v>
+        <v>-7.07830748</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1584658851717773</v>
+        <v>0.1619866940833953</v>
       </c>
       <c r="T69">
-        <v>1.550888317390086</v>
+        <v>1.599353577308526</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04308445069506359</v>
+        <v>0.04245085583190088</v>
       </c>
       <c r="W69">
-        <v>0.225640686526104</v>
+        <v>0.2257900881948378</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.287229671300424</v>
+        <v>0.283005705546006</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2053730020791762</v>
+        <v>0.2072730020791762</v>
       </c>
       <c r="C70">
-        <v>-28.27622216124264</v>
+        <v>-29.22855133345805</v>
       </c>
       <c r="D70">
-        <v>19.14977783875736</v>
+        <v>18.92444866654195</v>
       </c>
       <c r="E70">
-        <v>16.736</v>
+        <v>17.463</v>
       </c>
       <c r="F70">
-        <v>49.43600000000001</v>
+        <v>50.163</v>
       </c>
       <c r="G70">
         <v>2.01</v>
@@ -7027,37 +7027,37 @@
         <v>3.299</v>
       </c>
       <c r="M70">
-        <v>11.6570088</v>
+        <v>11.8284354</v>
       </c>
       <c r="N70">
-        <v>-8.3580088</v>
+        <v>-8.529435400000001</v>
       </c>
       <c r="O70">
-        <v>-1.25370132</v>
+        <v>-1.27941531</v>
       </c>
       <c r="P70">
-        <v>-7.10430748</v>
+        <v>-7.25002009</v>
       </c>
       <c r="Q70">
-        <v>-7.07830748</v>
+        <v>-7.224020090000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1619866940833953</v>
+        <v>0.1657346519570533</v>
       </c>
       <c r="T70">
-        <v>1.599353577308526</v>
+        <v>1.650945628189446</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04245085583190088</v>
+        <v>0.04183562603723565</v>
       </c>
       <c r="W70">
-        <v>0.2257900881948378</v>
+        <v>0.2259351593804198</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.283005705546006</v>
+        <v>0.2789041735815712</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2072730020791762</v>
+        <v>0.2091730020791762</v>
       </c>
       <c r="C71">
-        <v>-29.22855133345805</v>
+        <v>-30.17563942640383</v>
       </c>
       <c r="D71">
-        <v>18.92444866654195</v>
+        <v>18.70436057359618</v>
       </c>
       <c r="E71">
-        <v>17.463</v>
+        <v>18.19</v>
       </c>
       <c r="F71">
-        <v>50.163</v>
+        <v>50.89000000000001</v>
       </c>
       <c r="G71">
         <v>2.01</v>
@@ -7109,37 +7109,37 @@
         <v>3.299</v>
       </c>
       <c r="M71">
-        <v>11.8284354</v>
+        <v>11.999862</v>
       </c>
       <c r="N71">
-        <v>-8.529435400000001</v>
+        <v>-8.700862000000001</v>
       </c>
       <c r="O71">
-        <v>-1.27941531</v>
+        <v>-1.3051293</v>
       </c>
       <c r="P71">
-        <v>-7.25002009</v>
+        <v>-7.395732700000001</v>
       </c>
       <c r="Q71">
-        <v>-7.224020090000001</v>
+        <v>-7.369732700000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1657346519570533</v>
+        <v>0.169732473688955</v>
       </c>
       <c r="T71">
-        <v>1.650945628189446</v>
+        <v>1.705977149129094</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04183562603723565</v>
+        <v>0.04123797423670372</v>
       </c>
       <c r="W71">
-        <v>0.2259351593804198</v>
+        <v>0.2260760856749853</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2789041735815712</v>
+        <v>0.2749198282446915</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2091730020791762</v>
+        <v>0.2110730020791762</v>
       </c>
       <c r="C72">
-        <v>-30.17563942640383</v>
+        <v>-31.11766719647365</v>
       </c>
       <c r="D72">
-        <v>18.70436057359618</v>
+        <v>18.48933280352635</v>
       </c>
       <c r="E72">
-        <v>18.19</v>
+        <v>18.917</v>
       </c>
       <c r="F72">
-        <v>50.89000000000001</v>
+        <v>51.617</v>
       </c>
       <c r="G72">
         <v>2.01</v>
@@ -7191,37 +7191,37 @@
         <v>3.299</v>
       </c>
       <c r="M72">
-        <v>11.999862</v>
+        <v>12.1712886</v>
       </c>
       <c r="N72">
-        <v>-8.700862000000001</v>
+        <v>-8.872288600000001</v>
       </c>
       <c r="O72">
-        <v>-1.3051293</v>
+        <v>-1.33084329</v>
       </c>
       <c r="P72">
-        <v>-7.395732700000001</v>
+        <v>-7.541445310000001</v>
       </c>
       <c r="Q72">
-        <v>-7.369732700000001</v>
+        <v>-7.515445310000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.169732473688955</v>
+        <v>0.1740060072644362</v>
       </c>
       <c r="T72">
-        <v>1.705977149129094</v>
+        <v>1.764803947374925</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04123797423670372</v>
+        <v>0.04065715769815859</v>
       </c>
       <c r="W72">
-        <v>0.2260760856749853</v>
+        <v>0.2262130422147742</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2749198282446915</v>
+        <v>0.2710477179877241</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2110730020791762</v>
+        <v>0.2129730020791762</v>
       </c>
       <c r="C73">
-        <v>-31.11766719647365</v>
+        <v>-32.05480718253469</v>
       </c>
       <c r="D73">
-        <v>18.48933280352635</v>
+        <v>18.27919281746531</v>
       </c>
       <c r="E73">
-        <v>18.91699999999999</v>
+        <v>19.644</v>
       </c>
       <c r="F73">
-        <v>51.617</v>
+        <v>52.344</v>
       </c>
       <c r="G73">
         <v>2.01</v>
@@ -7273,37 +7273,37 @@
         <v>3.299</v>
       </c>
       <c r="M73">
-        <v>12.1712886</v>
+        <v>12.3427152</v>
       </c>
       <c r="N73">
-        <v>-8.872288600000001</v>
+        <v>-9.043715200000001</v>
       </c>
       <c r="O73">
-        <v>-1.33084329</v>
+        <v>-1.35655728</v>
       </c>
       <c r="P73">
-        <v>-7.541445310000001</v>
+        <v>-7.687157920000001</v>
       </c>
       <c r="Q73">
-        <v>-7.515445310000001</v>
+        <v>-7.661157920000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1740060072644362</v>
+        <v>0.1785847932381661</v>
       </c>
       <c r="T73">
-        <v>1.764803947374925</v>
+        <v>1.827832659781172</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04065715769815861</v>
+        <v>0.04009247495235084</v>
       </c>
       <c r="W73">
-        <v>0.2262130422147742</v>
+        <v>0.2263461944062357</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.271047717987724</v>
+        <v>0.2672831663490055</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2129730020791762</v>
+        <v>0.2148730020791762</v>
       </c>
       <c r="C74">
-        <v>-32.05480718253469</v>
+        <v>-32.98722416765995</v>
       </c>
       <c r="D74">
-        <v>18.27919281746531</v>
+        <v>18.07377583234004</v>
       </c>
       <c r="E74">
-        <v>19.644</v>
+        <v>20.371</v>
       </c>
       <c r="F74">
-        <v>52.344</v>
+        <v>53.071</v>
       </c>
       <c r="G74">
         <v>2.01</v>
@@ -7355,37 +7355,37 @@
         <v>3.299</v>
       </c>
       <c r="M74">
-        <v>12.3427152</v>
+        <v>12.5141418</v>
       </c>
       <c r="N74">
-        <v>-9.043715200000001</v>
+        <v>-9.215141800000001</v>
       </c>
       <c r="O74">
-        <v>-1.35655728</v>
+        <v>-1.38227127</v>
       </c>
       <c r="P74">
-        <v>-7.687157920000001</v>
+        <v>-7.832870530000001</v>
       </c>
       <c r="Q74">
-        <v>-7.661157920000001</v>
+        <v>-7.806870530000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1785847932381661</v>
+        <v>0.1835027485432834</v>
       </c>
       <c r="T74">
-        <v>1.827832659781172</v>
+        <v>1.895530165698993</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04009247495235084</v>
+        <v>0.0395432629667022</v>
       </c>
       <c r="W74">
-        <v>0.2263461944062357</v>
+        <v>0.2264756985924516</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2672831663490055</v>
+        <v>0.2636217531113479</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2148730020791762</v>
+        <v>0.2167730020791762</v>
       </c>
       <c r="C75">
-        <v>-32.98722416765995</v>
+        <v>-33.91507561007391</v>
       </c>
       <c r="D75">
-        <v>18.07377583234004</v>
+        <v>17.87292438992609</v>
       </c>
       <c r="E75">
-        <v>20.371</v>
+        <v>21.098</v>
       </c>
       <c r="F75">
-        <v>53.071</v>
+        <v>53.798</v>
       </c>
       <c r="G75">
         <v>2.01</v>
@@ -7437,37 +7437,37 @@
         <v>3.299</v>
       </c>
       <c r="M75">
-        <v>12.5141418</v>
+        <v>12.6855684</v>
       </c>
       <c r="N75">
-        <v>-9.215141800000001</v>
+        <v>-9.386568400000002</v>
       </c>
       <c r="O75">
-        <v>-1.38227127</v>
+        <v>-1.40798526</v>
       </c>
       <c r="P75">
-        <v>-7.832870530000001</v>
+        <v>-7.978583140000001</v>
       </c>
       <c r="Q75">
-        <v>-7.806870530000001</v>
+        <v>-7.952583140000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1835027485432834</v>
+        <v>0.1887990081026404</v>
       </c>
       <c r="T75">
-        <v>1.895530165698993</v>
+        <v>1.968435172072031</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0395432629667022</v>
+        <v>0.03900889454823325</v>
       </c>
       <c r="W75">
-        <v>0.2264756985924516</v>
+        <v>0.2266017026655266</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2636217531113479</v>
+        <v>0.2600592969882216</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2167730020791762</v>
+        <v>0.2186730020791762</v>
       </c>
       <c r="C76">
-        <v>-33.91507561007391</v>
+        <v>-34.83851204567945</v>
       </c>
       <c r="D76">
-        <v>17.87292438992609</v>
+        <v>17.67648795432056</v>
       </c>
       <c r="E76">
-        <v>21.098</v>
+        <v>21.825</v>
       </c>
       <c r="F76">
-        <v>53.798</v>
+        <v>54.52500000000001</v>
       </c>
       <c r="G76">
         <v>2.01</v>
@@ -7519,37 +7519,37 @@
         <v>3.299</v>
       </c>
       <c r="M76">
-        <v>12.6855684</v>
+        <v>12.856995</v>
       </c>
       <c r="N76">
-        <v>-9.386568400000002</v>
+        <v>-9.557995000000002</v>
       </c>
       <c r="O76">
-        <v>-1.40798526</v>
+        <v>-1.43369925</v>
       </c>
       <c r="P76">
-        <v>-7.978583140000001</v>
+        <v>-8.124295750000002</v>
       </c>
       <c r="Q76">
-        <v>-7.952583140000002</v>
+        <v>-8.098295750000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1887990081026404</v>
+        <v>0.194518968426746</v>
       </c>
       <c r="T76">
-        <v>1.968435172072031</v>
+        <v>2.047172578954913</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03900889454823325</v>
+        <v>0.03848877595425681</v>
       </c>
       <c r="W76">
-        <v>0.2266017026655266</v>
+        <v>0.2267243466299863</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2600592969882216</v>
+        <v>0.2565918396950453</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2186730020791762</v>
+        <v>0.2205730020791762</v>
       </c>
       <c r="C77">
-        <v>-34.83851204567945</v>
+        <v>-35.75767746432915</v>
       </c>
       <c r="D77">
-        <v>17.67648795432056</v>
+        <v>17.48432253567086</v>
       </c>
       <c r="E77">
-        <v>21.825</v>
+        <v>22.552</v>
       </c>
       <c r="F77">
-        <v>54.52500000000001</v>
+        <v>55.252</v>
       </c>
       <c r="G77">
         <v>2.01</v>
@@ -7601,37 +7601,37 @@
         <v>3.299</v>
       </c>
       <c r="M77">
-        <v>12.856995</v>
+        <v>13.0284216</v>
       </c>
       <c r="N77">
-        <v>-9.557995000000002</v>
+        <v>-9.729421600000002</v>
       </c>
       <c r="O77">
-        <v>-1.43369925</v>
+        <v>-1.45941324</v>
       </c>
       <c r="P77">
-        <v>-8.124295750000002</v>
+        <v>-8.270008360000002</v>
       </c>
       <c r="Q77">
-        <v>-8.098295750000002</v>
+        <v>-8.244008360000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.194518968426746</v>
+        <v>0.2007155921111938</v>
       </c>
       <c r="T77">
-        <v>2.047172578954913</v>
+        <v>2.132471436411368</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03848877595425681</v>
+        <v>0.0379823446917008</v>
       </c>
       <c r="W77">
-        <v>0.2267243466299863</v>
+        <v>0.226843763121697</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2565918396950453</v>
+        <v>0.2532156312780053</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2205730020791762</v>
+        <v>0.2224730020791762</v>
       </c>
       <c r="C78">
-        <v>-35.75767746432915</v>
+        <v>-36.67270966181727</v>
       </c>
       <c r="D78">
-        <v>17.48432253567086</v>
+        <v>17.29629033818273</v>
       </c>
       <c r="E78">
-        <v>22.552</v>
+        <v>23.279</v>
       </c>
       <c r="F78">
-        <v>55.252</v>
+        <v>55.97900000000001</v>
       </c>
       <c r="G78">
         <v>2.01</v>
@@ -7683,37 +7683,37 @@
         <v>3.299</v>
       </c>
       <c r="M78">
-        <v>13.0284216</v>
+        <v>13.1998482</v>
       </c>
       <c r="N78">
-        <v>-9.729421600000002</v>
+        <v>-9.900848200000002</v>
       </c>
       <c r="O78">
-        <v>-1.45941324</v>
+        <v>-1.48512723</v>
       </c>
       <c r="P78">
-        <v>-8.270008360000002</v>
+        <v>-8.415720970000002</v>
       </c>
       <c r="Q78">
-        <v>-8.244008360000002</v>
+        <v>-8.389720970000003</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2007155921111938</v>
+        <v>0.2074510526377674</v>
       </c>
       <c r="T78">
-        <v>2.132471436411368</v>
+        <v>2.225187585820557</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.0379823446917008</v>
+        <v>0.03748906748791248</v>
       </c>
       <c r="W78">
-        <v>0.226843763121697</v>
+        <v>0.2269600778863503</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2532156312780053</v>
+        <v>0.2499271165860831</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2224730020791762</v>
+        <v>0.2243730020791762</v>
       </c>
       <c r="C79">
-        <v>-36.67270966181727</v>
+        <v>-37.58374056940082</v>
       </c>
       <c r="D79">
-        <v>17.29629033818273</v>
+        <v>17.11225943059919</v>
       </c>
       <c r="E79">
-        <v>23.279</v>
+        <v>24.006</v>
       </c>
       <c r="F79">
-        <v>55.97900000000001</v>
+        <v>56.706</v>
       </c>
       <c r="G79">
         <v>2.01</v>
@@ -7765,37 +7765,37 @@
         <v>3.299</v>
       </c>
       <c r="M79">
-        <v>13.1998482</v>
+        <v>13.3712748</v>
       </c>
       <c r="N79">
-        <v>-9.900848200000002</v>
+        <v>-10.0722748</v>
       </c>
       <c r="O79">
-        <v>-1.48512723</v>
+        <v>-1.51084122</v>
       </c>
       <c r="P79">
-        <v>-8.415720970000002</v>
+        <v>-8.561433580000003</v>
       </c>
       <c r="Q79">
-        <v>-8.389720970000003</v>
+        <v>-8.535433580000003</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2074510526377674</v>
+        <v>0.214798827757666</v>
       </c>
       <c r="T79">
-        <v>2.225187585820557</v>
+        <v>2.326332476085128</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03748906748791248</v>
+        <v>0.03700843841755462</v>
       </c>
       <c r="W79">
-        <v>0.2269600778863503</v>
+        <v>0.2270734102211406</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2499271165860831</v>
+        <v>0.2467229227836975</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2243730020791762</v>
+        <v>0.2262730020791762</v>
       </c>
       <c r="C80">
-        <v>-37.58374056940082</v>
+        <v>-38.4908965625054</v>
       </c>
       <c r="D80">
-        <v>17.11225943059919</v>
+        <v>16.93210343749461</v>
       </c>
       <c r="E80">
-        <v>24.006</v>
+        <v>24.733</v>
       </c>
       <c r="F80">
-        <v>56.706</v>
+        <v>57.43300000000001</v>
       </c>
       <c r="G80">
         <v>2.01</v>
@@ -7847,37 +7847,37 @@
         <v>3.299</v>
       </c>
       <c r="M80">
-        <v>13.3712748</v>
+        <v>13.5427014</v>
       </c>
       <c r="N80">
-        <v>-10.0722748</v>
+        <v>-10.2437014</v>
       </c>
       <c r="O80">
-        <v>-1.51084122</v>
+        <v>-1.53655521</v>
       </c>
       <c r="P80">
-        <v>-8.561433580000003</v>
+        <v>-8.707146190000003</v>
       </c>
       <c r="Q80">
-        <v>-8.535433580000003</v>
+        <v>-8.681146190000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.214798827757666</v>
+        <v>0.2228463909842215</v>
       </c>
       <c r="T80">
-        <v>2.326332476085128</v>
+        <v>2.437110213041564</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03700843841755462</v>
+        <v>0.03653997717176279</v>
       </c>
       <c r="W80">
-        <v>0.2270734102211406</v>
+        <v>0.2271838733828983</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2467229227836975</v>
+        <v>0.2435998478117519</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2262730020791762</v>
+        <v>0.2281730020791762</v>
       </c>
       <c r="C81">
-        <v>-38.4908965625054</v>
+        <v>-39.39429875013443</v>
       </c>
       <c r="D81">
-        <v>16.93210343749461</v>
+        <v>16.75570124986557</v>
       </c>
       <c r="E81">
-        <v>24.733</v>
+        <v>25.46</v>
       </c>
       <c r="F81">
-        <v>57.43300000000001</v>
+        <v>58.16</v>
       </c>
       <c r="G81">
         <v>2.01</v>
@@ -7929,37 +7929,37 @@
         <v>3.299</v>
       </c>
       <c r="M81">
-        <v>13.5427014</v>
+        <v>13.714128</v>
       </c>
       <c r="N81">
-        <v>-10.2437014</v>
+        <v>-10.415128</v>
       </c>
       <c r="O81">
-        <v>-1.53655521</v>
+        <v>-1.5622692</v>
       </c>
       <c r="P81">
-        <v>-8.707146190000003</v>
+        <v>-8.852858800000002</v>
       </c>
       <c r="Q81">
-        <v>-8.681146190000003</v>
+        <v>-8.826858800000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2228463909842215</v>
+        <v>0.2316987105334326</v>
       </c>
       <c r="T81">
-        <v>2.437110213041564</v>
+        <v>2.558965723693642</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03653997717176279</v>
+        <v>0.03608322745711576</v>
       </c>
       <c r="W81">
-        <v>0.2271838733828983</v>
+        <v>0.2272915749656121</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2435998478117519</v>
+        <v>0.240554849714105</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2281730020791762</v>
+        <v>0.2300730020791762</v>
       </c>
       <c r="C82">
-        <v>-39.39429875013443</v>
+        <v>-40.29406324637389</v>
       </c>
       <c r="D82">
-        <v>16.75570124986557</v>
+        <v>16.58293675362612</v>
       </c>
       <c r="E82">
-        <v>25.46</v>
+        <v>26.187</v>
       </c>
       <c r="F82">
-        <v>58.16</v>
+        <v>58.88700000000001</v>
       </c>
       <c r="G82">
         <v>2.01</v>
@@ -8011,37 +8011,37 @@
         <v>3.299</v>
       </c>
       <c r="M82">
-        <v>13.714128</v>
+        <v>13.8855546</v>
       </c>
       <c r="N82">
-        <v>-10.415128</v>
+        <v>-10.5865546</v>
       </c>
       <c r="O82">
-        <v>-1.5622692</v>
+        <v>-1.58798319</v>
       </c>
       <c r="P82">
-        <v>-8.852858800000002</v>
+        <v>-8.998571410000002</v>
       </c>
       <c r="Q82">
-        <v>-8.826858800000002</v>
+        <v>-8.972571410000002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2316987105334326</v>
+        <v>0.2414828531930869</v>
       </c>
       <c r="T82">
-        <v>2.558965723693642</v>
+        <v>2.693648130203834</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03608322745711576</v>
+        <v>0.03563775551320075</v>
       </c>
       <c r="W82">
-        <v>0.2272915749656121</v>
+        <v>0.2273966172499873</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.240554849714105</v>
+        <v>0.2375850367546716</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2300730020791762</v>
+        <v>0.2319730020791762</v>
       </c>
       <c r="C83">
-        <v>-40.29406324637389</v>
+        <v>-41.19030142527209</v>
       </c>
       <c r="D83">
-        <v>16.58293675362612</v>
+        <v>16.41369857472792</v>
       </c>
       <c r="E83">
-        <v>26.187</v>
+        <v>26.914</v>
       </c>
       <c r="F83">
-        <v>58.88700000000001</v>
+        <v>59.614</v>
       </c>
       <c r="G83">
         <v>2.01</v>
@@ -8093,37 +8093,37 @@
         <v>3.299</v>
       </c>
       <c r="M83">
-        <v>13.8855546</v>
+        <v>14.0569812</v>
       </c>
       <c r="N83">
-        <v>-10.5865546</v>
+        <v>-10.7579812</v>
       </c>
       <c r="O83">
-        <v>-1.58798319</v>
+        <v>-1.61369718</v>
       </c>
       <c r="P83">
-        <v>-8.998571410000002</v>
+        <v>-9.144284020000001</v>
       </c>
       <c r="Q83">
-        <v>-8.972571410000002</v>
+        <v>-9.118284020000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2414828531930869</v>
+        <v>0.2523541228149251</v>
       </c>
       <c r="T83">
-        <v>2.693648130203834</v>
+        <v>2.843295248548491</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03563775551320075</v>
+        <v>0.03520314873864952</v>
       </c>
       <c r="W83">
-        <v>0.2273966172499873</v>
+        <v>0.2274990975274264</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2375850367546716</v>
+        <v>0.2346876582576636</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2319730020791762</v>
+        <v>0.2338730020791762</v>
       </c>
       <c r="C84">
-        <v>-41.19030142527209</v>
+        <v>-42.08312016026976</v>
       </c>
       <c r="D84">
-        <v>16.41369857472792</v>
+        <v>16.24787983973025</v>
       </c>
       <c r="E84">
-        <v>26.914</v>
+        <v>27.64100000000001</v>
       </c>
       <c r="F84">
-        <v>59.614</v>
+        <v>60.34100000000001</v>
       </c>
       <c r="G84">
         <v>2.01</v>
@@ -8175,37 +8175,37 @@
         <v>3.299</v>
       </c>
       <c r="M84">
-        <v>14.0569812</v>
+        <v>14.2284078</v>
       </c>
       <c r="N84">
-        <v>-10.7579812</v>
+        <v>-10.9294078</v>
       </c>
       <c r="O84">
-        <v>-1.61369718</v>
+        <v>-1.63941117</v>
       </c>
       <c r="P84">
-        <v>-9.144284020000001</v>
+        <v>-9.289996630000003</v>
       </c>
       <c r="Q84">
-        <v>-9.118284020000001</v>
+        <v>-9.263996630000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2523541228149251</v>
+        <v>0.2645043653334501</v>
       </c>
       <c r="T84">
-        <v>2.843295248548491</v>
+        <v>3.010547910227814</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03520314873864952</v>
+        <v>0.03477901441649711</v>
       </c>
       <c r="W84">
-        <v>0.2274990975274264</v>
+        <v>0.22759910840059</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2346876582576636</v>
+        <v>0.2318600961099807</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2338730020791762</v>
+        <v>0.2357730020791762</v>
       </c>
       <c r="C85">
-        <v>-42.08312016026976</v>
+        <v>-42.97262204926249</v>
       </c>
       <c r="D85">
-        <v>16.24787983973025</v>
+        <v>16.08537795073751</v>
       </c>
       <c r="E85">
-        <v>27.64100000000001</v>
+        <v>28.368</v>
       </c>
       <c r="F85">
-        <v>60.34100000000001</v>
+        <v>61.068</v>
       </c>
       <c r="G85">
         <v>2.01</v>
@@ -8257,37 +8257,37 @@
         <v>3.299</v>
       </c>
       <c r="M85">
-        <v>14.2284078</v>
+        <v>14.3998344</v>
       </c>
       <c r="N85">
-        <v>-10.9294078</v>
+        <v>-11.1008344</v>
       </c>
       <c r="O85">
-        <v>-1.63941117</v>
+        <v>-1.66512516</v>
       </c>
       <c r="P85">
-        <v>-9.289996630000003</v>
+        <v>-9.43570924</v>
       </c>
       <c r="Q85">
-        <v>-9.263996630000003</v>
+        <v>-9.40970924</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2645043653334501</v>
+        <v>0.2781733881667908</v>
       </c>
       <c r="T85">
-        <v>3.010547910227814</v>
+        <v>3.198707154617053</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03477901441649711</v>
+        <v>0.03436497853058643</v>
       </c>
       <c r="W85">
-        <v>0.22759910840059</v>
+        <v>0.2276967380624877</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2318600961099807</v>
+        <v>0.2290998568705763</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2357730020791762</v>
+        <v>0.2376730020791762</v>
       </c>
       <c r="C86">
-        <v>-42.9726220492625</v>
+        <v>-43.85890562629116</v>
       </c>
       <c r="D86">
-        <v>16.0853779507375</v>
+        <v>15.92609437370884</v>
       </c>
       <c r="E86">
-        <v>28.36799999999999</v>
+        <v>29.095</v>
       </c>
       <c r="F86">
-        <v>61.068</v>
+        <v>61.795</v>
       </c>
       <c r="G86">
         <v>2.01</v>
@@ -8339,37 +8339,37 @@
         <v>3.299</v>
       </c>
       <c r="M86">
-        <v>14.3998344</v>
+        <v>14.571261</v>
       </c>
       <c r="N86">
-        <v>-11.1008344</v>
+        <v>-11.272261</v>
       </c>
       <c r="O86">
-        <v>-1.66512516</v>
+        <v>-1.69083915</v>
       </c>
       <c r="P86">
-        <v>-9.43570924</v>
+        <v>-9.58142185</v>
       </c>
       <c r="Q86">
-        <v>-9.40970924</v>
+        <v>-9.55542185</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2781733881667906</v>
+        <v>0.29366494737791</v>
       </c>
       <c r="T86">
-        <v>3.198707154617051</v>
+        <v>3.411954298258188</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03436497853058644</v>
+        <v>0.03396068466552071</v>
       </c>
       <c r="W86">
-        <v>0.2276967380624877</v>
+        <v>0.2277920705558702</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2290998568705762</v>
+        <v>0.2264045644368048</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2376730020791762</v>
+        <v>0.2395730020791762</v>
       </c>
       <c r="C87">
-        <v>-43.85890562629116</v>
+        <v>-44.74206556077823</v>
       </c>
       <c r="D87">
-        <v>15.92609437370884</v>
+        <v>15.76993443922177</v>
       </c>
       <c r="E87">
-        <v>29.095</v>
+        <v>29.822</v>
       </c>
       <c r="F87">
-        <v>61.795</v>
+        <v>62.522</v>
       </c>
       <c r="G87">
         <v>2.01</v>
@@ -8421,37 +8421,37 @@
         <v>3.299</v>
       </c>
       <c r="M87">
-        <v>14.571261</v>
+        <v>14.7426876</v>
       </c>
       <c r="N87">
-        <v>-11.272261</v>
+        <v>-11.4436876</v>
       </c>
       <c r="O87">
-        <v>-1.69083915</v>
+        <v>-1.71655314</v>
       </c>
       <c r="P87">
-        <v>-9.58142185</v>
+        <v>-9.72713446</v>
       </c>
       <c r="Q87">
-        <v>-9.55542185</v>
+        <v>-9.70113446</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.29366494737791</v>
+        <v>0.3113695864763322</v>
       </c>
       <c r="T87">
-        <v>3.411954298258188</v>
+        <v>3.655665319562344</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03396068466552071</v>
+        <v>0.0335657929833635</v>
       </c>
       <c r="W87">
-        <v>0.2277920705558702</v>
+        <v>0.2278851860145229</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2264045644368048</v>
+        <v>0.2237719532224233</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2395730020791762</v>
+        <v>0.2414730020791762</v>
       </c>
       <c r="C88">
-        <v>-44.74206556077823</v>
+        <v>-45.62219284515648</v>
       </c>
       <c r="D88">
-        <v>15.76993443922177</v>
+        <v>15.61680715484352</v>
       </c>
       <c r="E88">
-        <v>29.822</v>
+        <v>30.549</v>
       </c>
       <c r="F88">
-        <v>62.522</v>
+        <v>63.249</v>
       </c>
       <c r="G88">
         <v>2.01</v>
@@ -8503,37 +8503,37 @@
         <v>3.299</v>
       </c>
       <c r="M88">
-        <v>14.7426876</v>
+        <v>14.9141142</v>
       </c>
       <c r="N88">
-        <v>-11.4436876</v>
+        <v>-11.6151142</v>
       </c>
       <c r="O88">
-        <v>-1.71655314</v>
+        <v>-1.74226713</v>
       </c>
       <c r="P88">
-        <v>-9.72713446</v>
+        <v>-9.872847070000001</v>
       </c>
       <c r="Q88">
-        <v>-9.70113446</v>
+        <v>-9.846847070000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3113695864763322</v>
+        <v>0.3317980162052808</v>
       </c>
       <c r="T88">
-        <v>3.655665319562344</v>
+        <v>3.936870344144063</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0335657929833635</v>
+        <v>0.03317997927091103</v>
       </c>
       <c r="W88">
-        <v>0.2278851860145229</v>
+        <v>0.2279761608879192</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2237719532224233</v>
+        <v>0.2211998618060736</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2414730020791762</v>
+        <v>0.2433730020791762</v>
       </c>
       <c r="C89">
-        <v>-45.62219284515648</v>
+        <v>-46.49937497167147</v>
       </c>
       <c r="D89">
-        <v>15.61680715484352</v>
+        <v>15.46662502832853</v>
       </c>
       <c r="E89">
-        <v>30.549</v>
+        <v>31.276</v>
       </c>
       <c r="F89">
-        <v>63.249</v>
+        <v>63.97600000000001</v>
       </c>
       <c r="G89">
         <v>2.01</v>
@@ -8585,37 +8585,37 @@
         <v>3.299</v>
       </c>
       <c r="M89">
-        <v>14.9141142</v>
+        <v>15.0855408</v>
       </c>
       <c r="N89">
-        <v>-11.6151142</v>
+        <v>-11.7865408</v>
       </c>
       <c r="O89">
-        <v>-1.74226713</v>
+        <v>-1.76798112</v>
       </c>
       <c r="P89">
-        <v>-9.872847070000001</v>
+        <v>-10.01855968</v>
       </c>
       <c r="Q89">
-        <v>-9.846847070000001</v>
+        <v>-9.992559680000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3317980162052808</v>
+        <v>0.3556311842223875</v>
       </c>
       <c r="T89">
-        <v>3.936870344144063</v>
+        <v>4.264942872822735</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03317997927091103</v>
+        <v>0.03280293405192341</v>
       </c>
       <c r="W89">
-        <v>0.2279761608879192</v>
+        <v>0.2280650681505565</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2211998618060736</v>
+        <v>0.2186862270128228</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2433730020791762</v>
+        <v>0.2452730020791762</v>
       </c>
       <c r="C90">
-        <v>-46.49937497167147</v>
+        <v>-47.37369609907977</v>
       </c>
       <c r="D90">
-        <v>15.46662502832853</v>
+        <v>15.31930390092023</v>
       </c>
       <c r="E90">
-        <v>31.276</v>
+        <v>32.003</v>
       </c>
       <c r="F90">
-        <v>63.97600000000001</v>
+        <v>64.703</v>
       </c>
       <c r="G90">
         <v>2.01</v>
@@ -8667,37 +8667,37 @@
         <v>3.299</v>
       </c>
       <c r="M90">
-        <v>15.0855408</v>
+        <v>15.2569674</v>
       </c>
       <c r="N90">
-        <v>-11.7865408</v>
+        <v>-11.9579674</v>
       </c>
       <c r="O90">
-        <v>-1.76798112</v>
+        <v>-1.79369511</v>
       </c>
       <c r="P90">
-        <v>-10.01855968</v>
+        <v>-10.16427229</v>
       </c>
       <c r="Q90">
-        <v>-9.992559680000001</v>
+        <v>-10.13827229</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3556311842223875</v>
+        <v>0.3837976555153319</v>
       </c>
       <c r="T90">
-        <v>4.264942872822735</v>
+        <v>4.652664952170257</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03280293405192341</v>
+        <v>0.03243436175920517</v>
       </c>
       <c r="W90">
-        <v>0.2280650681505565</v>
+        <v>0.2281519774971794</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2186862270128228</v>
+        <v>0.2162290783947011</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2452730020791762</v>
+        <v>0.2471730020791762</v>
       </c>
       <c r="C91">
-        <v>-47.37369609907977</v>
+        <v>-48.24523720991004</v>
       </c>
       <c r="D91">
-        <v>15.31930390092023</v>
+        <v>15.17476279008997</v>
       </c>
       <c r="E91">
-        <v>32.003</v>
+        <v>32.73</v>
       </c>
       <c r="F91">
-        <v>64.703</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="G91">
         <v>2.01</v>
@@ -8749,37 +8749,37 @@
         <v>3.299</v>
       </c>
       <c r="M91">
-        <v>15.2569674</v>
+        <v>15.428394</v>
       </c>
       <c r="N91">
-        <v>-11.9579674</v>
+        <v>-12.129394</v>
       </c>
       <c r="O91">
-        <v>-1.79369511</v>
+        <v>-1.8194091</v>
       </c>
       <c r="P91">
-        <v>-10.16427229</v>
+        <v>-10.3099849</v>
       </c>
       <c r="Q91">
-        <v>-10.13827229</v>
+        <v>-10.2839849</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3837976555153319</v>
+        <v>0.4175974210668651</v>
       </c>
       <c r="T91">
-        <v>4.652664952170257</v>
+        <v>5.117931447387283</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03243436175920517</v>
+        <v>0.03207397996188067</v>
       </c>
       <c r="W91">
-        <v>0.2281519774971794</v>
+        <v>0.2282369555249885</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2162290783947011</v>
+        <v>0.2138265330792045</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2471730020791762</v>
+        <v>0.2490730020791762</v>
       </c>
       <c r="C92">
-        <v>-48.24523720991004</v>
+        <v>-49.11407625890456</v>
       </c>
       <c r="D92">
-        <v>15.17476279008997</v>
+        <v>15.03292374109545</v>
       </c>
       <c r="E92">
-        <v>32.73</v>
+        <v>33.45700000000001</v>
       </c>
       <c r="F92">
-        <v>65.43000000000001</v>
+        <v>66.15700000000001</v>
       </c>
       <c r="G92">
         <v>2.01</v>
@@ -8831,37 +8831,37 @@
         <v>3.299</v>
       </c>
       <c r="M92">
-        <v>15.428394</v>
+        <v>15.5998206</v>
       </c>
       <c r="N92">
-        <v>-12.129394</v>
+        <v>-12.3008206</v>
       </c>
       <c r="O92">
-        <v>-1.8194091</v>
+        <v>-1.84512309</v>
       </c>
       <c r="P92">
-        <v>-10.3099849</v>
+        <v>-10.45569751</v>
       </c>
       <c r="Q92">
-        <v>-10.2839849</v>
+        <v>-10.42969751</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4175974210668651</v>
+        <v>0.4589082456298502</v>
       </c>
       <c r="T92">
-        <v>5.117931447387283</v>
+        <v>5.686590497096982</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03207397996188067</v>
+        <v>0.03172151864361825</v>
       </c>
       <c r="W92">
-        <v>0.2282369555249885</v>
+        <v>0.2283200659038348</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2138265330792045</v>
+        <v>0.211476790957455</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2490730020791762</v>
+        <v>0.2509730020791762</v>
       </c>
       <c r="C93">
-        <v>-49.11407625890456</v>
+        <v>-49.98028831321304</v>
       </c>
       <c r="D93">
-        <v>15.03292374109545</v>
+        <v>14.89371168678697</v>
       </c>
       <c r="E93">
-        <v>33.45700000000001</v>
+        <v>34.184</v>
       </c>
       <c r="F93">
-        <v>66.15700000000001</v>
+        <v>66.884</v>
       </c>
       <c r="G93">
         <v>2.01</v>
@@ -8913,37 +8913,37 @@
         <v>3.299</v>
       </c>
       <c r="M93">
-        <v>15.5998206</v>
+        <v>15.7712472</v>
       </c>
       <c r="N93">
-        <v>-12.3008206</v>
+        <v>-12.4722472</v>
       </c>
       <c r="O93">
-        <v>-1.84512309</v>
+        <v>-1.87083708</v>
       </c>
       <c r="P93">
-        <v>-10.45569751</v>
+        <v>-10.60141012</v>
       </c>
       <c r="Q93">
-        <v>-10.42969751</v>
+        <v>-10.57541012</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4589082456298502</v>
+        <v>0.5105467763335815</v>
       </c>
       <c r="T93">
-        <v>5.686590497096982</v>
+        <v>6.397414309234106</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03172151864361825</v>
+        <v>0.03137671952792675</v>
       </c>
       <c r="W93">
-        <v>0.2283200659038348</v>
+        <v>0.2284013695353149</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.211476790957455</v>
+        <v>0.2091781301861783</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2509730020791762</v>
+        <v>0.2528730020791762</v>
       </c>
       <c r="C94">
-        <v>-49.98028831321304</v>
+        <v>-50.84394568486826</v>
       </c>
       <c r="D94">
-        <v>14.89371168678697</v>
+        <v>14.75705431513175</v>
       </c>
       <c r="E94">
-        <v>34.184</v>
+        <v>34.911</v>
       </c>
       <c r="F94">
-        <v>66.884</v>
+        <v>67.611</v>
       </c>
       <c r="G94">
         <v>2.01</v>
@@ -8995,37 +8995,37 @@
         <v>3.299</v>
       </c>
       <c r="M94">
-        <v>15.7712472</v>
+        <v>15.9426738</v>
       </c>
       <c r="N94">
-        <v>-12.4722472</v>
+        <v>-12.6436738</v>
       </c>
       <c r="O94">
-        <v>-1.87083708</v>
+        <v>-1.89655107</v>
       </c>
       <c r="P94">
-        <v>-10.60141012</v>
+        <v>-10.74712273</v>
       </c>
       <c r="Q94">
-        <v>-10.57541012</v>
+        <v>-10.72112273</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5105467763335815</v>
+        <v>0.5769391729526645</v>
       </c>
       <c r="T94">
-        <v>6.397414309234106</v>
+        <v>7.311330639124693</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03137671952792675</v>
+        <v>0.0310393354469813</v>
       </c>
       <c r="W94">
-        <v>0.2284013695353149</v>
+        <v>0.2284809247016018</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2091781301861783</v>
+        <v>0.2069289029798752</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2528730020791762</v>
+        <v>0.2547730020791762</v>
       </c>
       <c r="C95">
-        <v>-50.84394568486826</v>
+        <v>-51.70511805603478</v>
       </c>
       <c r="D95">
-        <v>14.75705431513175</v>
+        <v>14.62288194396523</v>
       </c>
       <c r="E95">
-        <v>34.911</v>
+        <v>35.63800000000001</v>
       </c>
       <c r="F95">
-        <v>67.611</v>
+        <v>68.33800000000001</v>
       </c>
       <c r="G95">
         <v>2.01</v>
@@ -9077,37 +9077,37 @@
         <v>3.299</v>
       </c>
       <c r="M95">
-        <v>15.9426738</v>
+        <v>16.1141004</v>
       </c>
       <c r="N95">
-        <v>-12.6436738</v>
+        <v>-12.8151004</v>
       </c>
       <c r="O95">
-        <v>-1.89655107</v>
+        <v>-1.92226506</v>
       </c>
       <c r="P95">
-        <v>-10.74712273</v>
+        <v>-10.89283534</v>
       </c>
       <c r="Q95">
-        <v>-10.72112273</v>
+        <v>-10.86683534</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5769391729526645</v>
+        <v>0.6654623684447756</v>
       </c>
       <c r="T95">
-        <v>7.311330639124693</v>
+        <v>8.529885745645478</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0310393354469813</v>
+        <v>0.03070912975073681</v>
       </c>
       <c r="W95">
-        <v>0.2284809247016018</v>
+        <v>0.2285587872047763</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2069289029798752</v>
+        <v>0.2047275316715788</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2547730020791762</v>
+        <v>0.2566730020791762</v>
       </c>
       <c r="C96">
-        <v>-51.70511805603478</v>
+        <v>-52.56387259748672</v>
       </c>
       <c r="D96">
-        <v>14.62288194396523</v>
+        <v>14.49112740251329</v>
       </c>
       <c r="E96">
-        <v>35.63800000000001</v>
+        <v>36.36500000000001</v>
       </c>
       <c r="F96">
-        <v>68.33800000000001</v>
+        <v>69.06500000000001</v>
       </c>
       <c r="G96">
         <v>2.01</v>
@@ -9159,37 +9159,37 @@
         <v>3.299</v>
       </c>
       <c r="M96">
-        <v>16.1141004</v>
+        <v>16.285527</v>
       </c>
       <c r="N96">
-        <v>-12.8151004</v>
+        <v>-12.986527</v>
       </c>
       <c r="O96">
-        <v>-1.92226506</v>
+        <v>-1.94797905</v>
       </c>
       <c r="P96">
-        <v>-10.89283534</v>
+        <v>-11.03854795</v>
       </c>
       <c r="Q96">
-        <v>-10.86683534</v>
+        <v>-11.01254795</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6654623684447756</v>
+        <v>0.789394842133731</v>
       </c>
       <c r="T96">
-        <v>8.529885745645478</v>
+        <v>10.23586289477458</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03070912975073681</v>
+        <v>0.03038587575336064</v>
       </c>
       <c r="W96">
-        <v>0.2285587872047763</v>
+        <v>0.2286350104973576</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2047275316715788</v>
+        <v>0.2025725050224042</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2566730020791762</v>
+        <v>0.2585730020791762</v>
       </c>
       <c r="C97">
-        <v>-52.56387259748672</v>
+        <v>-53.42027408073753</v>
       </c>
       <c r="D97">
-        <v>14.49112740251329</v>
+        <v>14.36172591926247</v>
       </c>
       <c r="E97">
-        <v>36.36500000000001</v>
+        <v>37.092</v>
       </c>
       <c r="F97">
-        <v>69.06500000000001</v>
+        <v>69.792</v>
       </c>
       <c r="G97">
         <v>2.01</v>
@@ -9241,37 +9241,37 @@
         <v>3.299</v>
       </c>
       <c r="M97">
-        <v>16.285527</v>
+        <v>16.4569536</v>
       </c>
       <c r="N97">
-        <v>-12.986527</v>
+        <v>-13.1579536</v>
       </c>
       <c r="O97">
-        <v>-1.94797905</v>
+        <v>-1.97369304</v>
       </c>
       <c r="P97">
-        <v>-11.03854795</v>
+        <v>-11.18426056</v>
       </c>
       <c r="Q97">
-        <v>-11.01254795</v>
+        <v>-11.15826056</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.789394842133731</v>
+        <v>0.9752935526671643</v>
       </c>
       <c r="T97">
-        <v>10.23586289477458</v>
+        <v>12.79482861846823</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03038587575336064</v>
+        <v>0.03006935621426313</v>
       </c>
       <c r="W97">
-        <v>0.2286350104973576</v>
+        <v>0.2287096458046768</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2025725050224042</v>
+        <v>0.2004623747617541</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2585730020791762</v>
+        <v>0.2604730020791762</v>
       </c>
       <c r="C98">
-        <v>-53.42027408073753</v>
+        <v>-54.27438498421544</v>
       </c>
       <c r="D98">
-        <v>14.36172591926247</v>
+        <v>14.23461501578457</v>
       </c>
       <c r="E98">
-        <v>37.092</v>
+        <v>37.819</v>
       </c>
       <c r="F98">
-        <v>69.792</v>
+        <v>70.51900000000001</v>
       </c>
       <c r="G98">
         <v>2.01</v>
@@ -9323,37 +9323,37 @@
         <v>3.299</v>
       </c>
       <c r="M98">
-        <v>16.4569536</v>
+        <v>16.6283802</v>
       </c>
       <c r="N98">
-        <v>-13.1579536</v>
+        <v>-13.3293802</v>
       </c>
       <c r="O98">
-        <v>-1.97369304</v>
+        <v>-1.99940703</v>
       </c>
       <c r="P98">
-        <v>-11.18426056</v>
+        <v>-11.32997317</v>
       </c>
       <c r="Q98">
-        <v>-11.15826056</v>
+        <v>-11.30397317</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9752935526671618</v>
+        <v>1.285124736889549</v>
       </c>
       <c r="T98">
-        <v>12.79482861846819</v>
+        <v>17.05977149129093</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03006935621426313</v>
+        <v>0.02975936285122949</v>
       </c>
       <c r="W98">
-        <v>0.2287096458046768</v>
+        <v>0.2287827422396801</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2004623747617541</v>
+        <v>0.1983957523415298</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2604730020791762</v>
+        <v>0.2623730020791762</v>
       </c>
       <c r="C99">
-        <v>-54.27438498421544</v>
+        <v>-55.12626559384979</v>
       </c>
       <c r="D99">
-        <v>14.23461501578457</v>
+        <v>14.10973440615021</v>
       </c>
       <c r="E99">
-        <v>37.819</v>
+        <v>38.54599999999999</v>
       </c>
       <c r="F99">
-        <v>70.51900000000001</v>
+        <v>71.246</v>
       </c>
       <c r="G99">
         <v>2.01</v>
@@ -9405,37 +9405,37 @@
         <v>3.299</v>
       </c>
       <c r="M99">
-        <v>16.6283802</v>
+        <v>16.7998068</v>
       </c>
       <c r="N99">
-        <v>-13.3293802</v>
+        <v>-13.5008068</v>
       </c>
       <c r="O99">
-        <v>-1.99940703</v>
+        <v>-2.02512102</v>
       </c>
       <c r="P99">
-        <v>-11.32997317</v>
+        <v>-11.47568578</v>
       </c>
       <c r="Q99">
-        <v>-11.30397317</v>
+        <v>-11.44968578</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.285124736889549</v>
+        <v>1.904787105334324</v>
       </c>
       <c r="T99">
-        <v>17.05977149129093</v>
+        <v>25.58965723693639</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02975936285122949</v>
+        <v>0.02945569588335981</v>
       </c>
       <c r="W99">
-        <v>0.2287827422396801</v>
+        <v>0.2288543469107037</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1983957523415298</v>
+        <v>0.1963713058890654</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2623730020791762</v>
+        <v>0.2642730020791762</v>
       </c>
       <c r="C100">
-        <v>-55.12626559384979</v>
+        <v>-55.97597409840895</v>
       </c>
       <c r="D100">
-        <v>14.10973440615021</v>
+        <v>13.98702590159104</v>
       </c>
       <c r="E100">
-        <v>38.54599999999999</v>
+        <v>39.273</v>
       </c>
       <c r="F100">
-        <v>71.246</v>
+        <v>71.973</v>
       </c>
       <c r="G100">
         <v>2.01</v>
@@ -9487,37 +9487,37 @@
         <v>3.299</v>
       </c>
       <c r="M100">
-        <v>16.7998068</v>
+        <v>16.9712334</v>
       </c>
       <c r="N100">
-        <v>-13.5008068</v>
+        <v>-13.6722334</v>
       </c>
       <c r="O100">
-        <v>-2.02512102</v>
+        <v>-2.05083501</v>
       </c>
       <c r="P100">
-        <v>-11.47568578</v>
+        <v>-11.62139839</v>
       </c>
       <c r="Q100">
-        <v>-11.44968578</v>
+        <v>-11.59539839</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.904787105334324</v>
+        <v>3.763774210668647</v>
       </c>
       <c r="T100">
-        <v>25.58965723693639</v>
+        <v>51.17931447387278</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02945569588335981</v>
+        <v>0.0291581636017097</v>
       </c>
       <c r="W100">
-        <v>0.2288543469107037</v>
+        <v>0.2289245050227169</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1963713058890654</v>
+        <v>0.1943877573447313</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2642730020791762</v>
-      </c>
-      <c r="C101">
-        <v>-55.97597409840895</v>
-      </c>
-      <c r="D101">
-        <v>13.98702590159104</v>
-      </c>
-      <c r="E101">
-        <v>39.273</v>
-      </c>
-      <c r="F101">
-        <v>71.973</v>
-      </c>
-      <c r="G101">
-        <v>2.01</v>
-      </c>
-      <c r="H101">
-        <v>40</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.325</v>
-      </c>
-      <c r="K101">
-        <v>0.026</v>
-      </c>
-      <c r="L101">
-        <v>3.299</v>
-      </c>
-      <c r="M101">
-        <v>16.9712334</v>
-      </c>
-      <c r="N101">
-        <v>-13.6722334</v>
-      </c>
-      <c r="O101">
-        <v>-2.05083501</v>
-      </c>
-      <c r="P101">
-        <v>-11.62139839</v>
-      </c>
-      <c r="Q101">
-        <v>-11.59539839</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.763774210668647</v>
-      </c>
-      <c r="T101">
-        <v>51.17931447387278</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0291581636017097</v>
-      </c>
-      <c r="W101">
-        <v>0.2289245050227169</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1943877573447313</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
